--- a/Aarong.xlsx
+++ b/Aarong.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SQA\Manual testing\Class-02_ M.T(28.2.26)\content\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SQA\Manual testing\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A23148-C17B-4CF9-B579-548571059644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B083310-A556-4C52-B961-A708F941B5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Plan" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="331">
   <si>
     <t>Please Click Here to show my testplan full PDF.</t>
   </si>
@@ -369,16 +369,6 @@
     </r>
   </si>
   <si>
-    <t>1. Goto the URL
-https://www.startech.com.bd
-2. Click on the Login button at the right corner
-3. Fill all the fields with invalid credentials
-4. Click ''Forgotten Password?"</t>
-  </si>
-  <si>
-    <t>Module: Login</t>
-  </si>
-  <si>
     <t>4. Click 'Continue'.</t>
   </si>
   <si>
@@ -386,78 +376,6 @@
   </si>
   <si>
     <t xml:space="preserve">Screenshot: First name error </t>
-  </si>
-  <si>
-    <t># SL 05</t>
-  </si>
-  <si>
-    <t>issue: A comma should not be expected between the name field.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Env:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Production</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Severity:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> P6</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Screenshot: Comma  error in first name. </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Responsible QA:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Tashfiquzzaman</t>
-    </r>
   </si>
   <si>
     <t>Test Metrics</t>
@@ -4170,20 +4088,107 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4227,112 +4232,26 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4344,6 +4263,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="47" fillId="21" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4352,6 +4276,8 @@
     <xf numFmtId="0" fontId="33" fillId="30" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="30" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -4359,35 +4285,18 @@
     <xf numFmtId="0" fontId="30" fillId="32" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="32" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="32" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="14" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="33" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="33" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="33" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4395,9 +4304,18 @@
     <xf numFmtId="0" fontId="49" fillId="28" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="33" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="33" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="52" fillId="35" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6227,7 +6145,7 @@
     <row r="14" spans="25:25" ht="12.75" customHeight="1"/>
     <row r="15" spans="25:25" ht="12.75" customHeight="1">
       <c r="Y15" s="302" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="25:25" ht="12.75" customHeight="1"/>
@@ -7334,7 +7252,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="409" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C4" s="410"/>
       <c r="D4" s="14"/>
@@ -7398,7 +7316,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="411" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C6" s="410"/>
       <c r="D6" s="14"/>
@@ -7641,7 +7559,7 @@
     </row>
     <row r="14" spans="1:26" ht="12.75" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="29" t="s">
@@ -7677,11 +7595,11 @@
     </row>
     <row r="15" spans="1:26" ht="12.75" customHeight="1">
       <c r="A15" s="349" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B15" s="28"/>
       <c r="C15" s="30" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>14</v>
@@ -7741,11 +7659,11 @@
     </row>
     <row r="17" spans="1:26" ht="12.75" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="30" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D17" s="36" t="s">
         <v>13</v>
@@ -7805,11 +7723,11 @@
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="30" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D19" s="36" t="s">
         <v>14</v>
@@ -7869,11 +7787,11 @@
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
       <c r="A21" s="27" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="30" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D21" s="36" t="s">
         <v>14</v>
@@ -35379,12 +35297,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A1" s="413" t="s">
+      <c r="A1" s="461" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="414"/>
+      <c r="B1" s="446"/>
       <c r="C1" s="329" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D1" s="225" t="s">
         <v>16</v>
@@ -35404,10 +35322,10 @@
       <c r="J1" s="42"/>
       <c r="K1" s="169"/>
       <c r="L1" s="43"/>
-      <c r="M1" s="415" t="s">
+      <c r="M1" s="462" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="416"/>
+      <c r="N1" s="463"/>
       <c r="O1" s="43"/>
       <c r="P1" s="43"/>
       <c r="Q1" s="43"/>
@@ -35426,12 +35344,12 @@
       <c r="AD1" s="43"/>
     </row>
     <row r="2" spans="1:30" ht="29.25" thickBot="1">
-      <c r="A2" s="413" t="s">
+      <c r="A2" s="461" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="414"/>
+      <c r="B2" s="446"/>
       <c r="C2" s="330" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D2" s="226" t="s">
         <v>20</v>
@@ -35475,17 +35393,17 @@
       <c r="AD2" s="43"/>
     </row>
     <row r="3" spans="1:30" ht="30.75" thickBot="1">
-      <c r="A3" s="413" t="s">
+      <c r="A3" s="461" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="414"/>
+      <c r="B3" s="446"/>
       <c r="C3" s="330"/>
       <c r="D3" s="226" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="353"/>
       <c r="F3" s="209" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G3" s="226" t="s">
         <v>26</v>
@@ -35522,17 +35440,17 @@
       <c r="AD3" s="43"/>
     </row>
     <row r="4" spans="1:30" ht="30.75" thickBot="1">
-      <c r="A4" s="413" t="s">
+      <c r="A4" s="461" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="414"/>
+      <c r="B4" s="446"/>
       <c r="C4" s="330"/>
       <c r="D4" s="226" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="353"/>
       <c r="F4" s="209" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G4" s="226" t="s">
         <v>31</v>
@@ -35569,18 +35487,18 @@
       <c r="AD4" s="43"/>
     </row>
     <row r="5" spans="1:30" ht="13.5" thickBot="1">
-      <c r="A5" s="417" t="s">
+      <c r="A5" s="445" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="414"/>
-      <c r="C5" s="418" t="s">
+      <c r="B5" s="446"/>
+      <c r="C5" s="447" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="419"/>
-      <c r="E5" s="420"/>
-      <c r="F5" s="419"/>
-      <c r="G5" s="419"/>
-      <c r="H5" s="414"/>
+      <c r="D5" s="448"/>
+      <c r="E5" s="449"/>
+      <c r="F5" s="448"/>
+      <c r="G5" s="448"/>
+      <c r="H5" s="446"/>
       <c r="I5" s="276"/>
       <c r="J5" s="48"/>
       <c r="K5" s="171"/>
@@ -35653,13 +35571,13 @@
         <v>38</v>
       </c>
       <c r="C7" s="332" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D7" s="211" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="354" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F7" s="211" t="s">
         <v>40</v>
@@ -35703,26 +35621,26 @@
       <c r="A8" s="61">
         <v>1</v>
       </c>
-      <c r="B8" s="429" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="427" t="s">
+      <c r="B8" s="458" t="s">
         <v>153</v>
       </c>
+      <c r="C8" s="456" t="s">
+        <v>145</v>
+      </c>
       <c r="D8" s="295" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E8" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F8" s="168" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G8" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H8" s="248" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I8" s="274"/>
       <c r="J8" s="175" t="s">
@@ -35751,22 +35669,22 @@
       <c r="A9" s="61">
         <v>2</v>
       </c>
-      <c r="B9" s="430"/>
-      <c r="C9" s="422"/>
+      <c r="B9" s="459"/>
+      <c r="C9" s="451"/>
       <c r="D9" s="295" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E9" s="203" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F9" s="168" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G9" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H9" s="248" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I9" s="274"/>
       <c r="J9" s="175" t="s">
@@ -35795,22 +35713,22 @@
       <c r="A10" s="61">
         <v>3</v>
       </c>
-      <c r="B10" s="430"/>
-      <c r="C10" s="422"/>
+      <c r="B10" s="459"/>
+      <c r="C10" s="451"/>
       <c r="D10" s="295" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E10" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F10" s="168" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G10" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H10" s="248" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="I10" s="274"/>
       <c r="J10" s="175" t="s">
@@ -35839,28 +35757,28 @@
       <c r="A11" s="61">
         <v>4</v>
       </c>
-      <c r="B11" s="430"/>
-      <c r="C11" s="422"/>
+      <c r="B11" s="459"/>
+      <c r="C11" s="451"/>
       <c r="D11" s="295" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E11" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F11" s="168" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G11" s="168" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H11" s="248" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I11" s="327" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="J11" s="175" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K11" s="65"/>
       <c r="L11" s="198"/>
@@ -35885,16 +35803,16 @@
       <c r="A12" s="61">
         <v>5</v>
       </c>
-      <c r="B12" s="430"/>
-      <c r="C12" s="422"/>
+      <c r="B12" s="459"/>
+      <c r="C12" s="451"/>
       <c r="D12" s="295" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="E12" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F12" s="168" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G12" s="168" t="s">
         <v>47</v>
@@ -35929,24 +35847,24 @@
       <c r="A13" s="61">
         <v>6</v>
       </c>
-      <c r="B13" s="430"/>
-      <c r="C13" s="427" t="s">
-        <v>155</v>
+      <c r="B13" s="459"/>
+      <c r="C13" s="456" t="s">
+        <v>147</v>
       </c>
       <c r="D13" s="295" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E13" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F13" s="168" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G13" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H13" s="248" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I13" s="274"/>
       <c r="J13" s="175" t="s">
@@ -35975,22 +35893,22 @@
       <c r="A14" s="61">
         <v>7</v>
       </c>
-      <c r="B14" s="430"/>
-      <c r="C14" s="422"/>
+      <c r="B14" s="459"/>
+      <c r="C14" s="451"/>
       <c r="D14" s="295" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E14" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F14" s="168" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G14" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H14" s="248" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I14" s="274"/>
       <c r="J14" s="175" t="s">
@@ -36019,22 +35937,22 @@
       <c r="A15" s="61">
         <v>8</v>
       </c>
-      <c r="B15" s="430"/>
-      <c r="C15" s="422"/>
+      <c r="B15" s="459"/>
+      <c r="C15" s="451"/>
       <c r="D15" s="295" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E15" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F15" s="168" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G15" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="248" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I15" s="274"/>
       <c r="J15" s="175" t="s">
@@ -36063,22 +35981,22 @@
       <c r="A16" s="61">
         <v>9</v>
       </c>
-      <c r="B16" s="430"/>
-      <c r="C16" s="422"/>
+      <c r="B16" s="459"/>
+      <c r="C16" s="451"/>
       <c r="D16" s="295" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E16" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F16" s="168" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G16" s="168" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H16" s="248" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="I16" s="274"/>
       <c r="J16" s="175" t="s">
@@ -36107,16 +36025,16 @@
       <c r="A17" s="61">
         <v>10</v>
       </c>
-      <c r="B17" s="430"/>
-      <c r="C17" s="428"/>
+      <c r="B17" s="459"/>
+      <c r="C17" s="457"/>
       <c r="D17" s="295" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E17" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F17" s="168" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G17" s="168" t="s">
         <v>47</v>
@@ -36151,24 +36069,24 @@
       <c r="A18" s="174">
         <v>11</v>
       </c>
-      <c r="B18" s="430"/>
-      <c r="C18" s="424" t="s">
-        <v>160</v>
+      <c r="B18" s="459"/>
+      <c r="C18" s="453" t="s">
+        <v>152</v>
       </c>
       <c r="D18" s="204" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="E18" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F18" s="57" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G18" s="57" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="253" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="I18" s="278"/>
       <c r="J18" s="175" t="s">
@@ -36197,22 +36115,22 @@
       <c r="A19" s="174">
         <v>12</v>
       </c>
-      <c r="B19" s="430"/>
-      <c r="C19" s="425"/>
+      <c r="B19" s="459"/>
+      <c r="C19" s="454"/>
       <c r="D19" s="205" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E19" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F19" s="57" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G19" s="57" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="253" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="I19" s="278"/>
       <c r="J19" s="175" t="s">
@@ -36241,22 +36159,22 @@
       <c r="A20" s="174">
         <v>13</v>
       </c>
-      <c r="B20" s="430"/>
-      <c r="C20" s="425"/>
+      <c r="B20" s="459"/>
+      <c r="C20" s="454"/>
       <c r="D20" s="206" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E20" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F20" s="212" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G20" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="254" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I20" s="279"/>
       <c r="J20" s="175" t="s">
@@ -36286,22 +36204,22 @@
       <c r="A21" s="328">
         <v>14</v>
       </c>
-      <c r="B21" s="430"/>
-      <c r="C21" s="425"/>
+      <c r="B21" s="459"/>
+      <c r="C21" s="454"/>
       <c r="D21" s="206" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E21" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F21" s="212" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G21" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H21" s="254" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="I21" s="279"/>
       <c r="J21" s="175" t="s">
@@ -36331,16 +36249,16 @@
       <c r="A22" s="174">
         <v>15</v>
       </c>
-      <c r="B22" s="430"/>
-      <c r="C22" s="425"/>
+      <c r="B22" s="459"/>
+      <c r="C22" s="454"/>
       <c r="D22" s="201" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E22" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F22" s="168" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G22" s="168" t="s">
         <v>47</v>
@@ -36376,22 +36294,22 @@
       <c r="A23" s="174">
         <v>16</v>
       </c>
-      <c r="B23" s="430"/>
-      <c r="C23" s="426"/>
+      <c r="B23" s="459"/>
+      <c r="C23" s="455"/>
       <c r="D23" s="201" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="E23" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F23" s="168" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G23" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H23" s="254" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="I23" s="279"/>
       <c r="J23" s="175" t="s">
@@ -36421,18 +36339,18 @@
       <c r="A24" s="174">
         <v>17</v>
       </c>
-      <c r="B24" s="430"/>
-      <c r="C24" s="421" t="s">
-        <v>149</v>
+      <c r="B24" s="459"/>
+      <c r="C24" s="450" t="s">
+        <v>141</v>
       </c>
       <c r="D24" s="201" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E24" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F24" s="168" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G24" s="168" t="s">
         <v>47</v>
@@ -36467,16 +36385,16 @@
       <c r="A25" s="328">
         <v>18</v>
       </c>
-      <c r="B25" s="430"/>
-      <c r="C25" s="422"/>
+      <c r="B25" s="459"/>
+      <c r="C25" s="451"/>
       <c r="D25" s="201" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E25" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F25" s="168" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="G25" s="168" t="s">
         <v>47</v>
@@ -36511,16 +36429,16 @@
       <c r="A26" s="174">
         <v>19</v>
       </c>
-      <c r="B26" s="431"/>
-      <c r="C26" s="423"/>
+      <c r="B26" s="460"/>
+      <c r="C26" s="452"/>
       <c r="D26" s="343" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E26" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F26" s="168" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G26" s="168" t="s">
         <v>47</v>
@@ -36557,22 +36475,22 @@
       </c>
       <c r="B27" s="316"/>
       <c r="C27" s="345" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D27" s="344" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E27" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F27" s="168" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G27" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H27" s="255" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="I27" s="274"/>
       <c r="J27" s="175" t="s">
@@ -36606,13 +36524,13 @@
       <c r="B28" s="316"/>
       <c r="C28" s="345"/>
       <c r="D28" s="344" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E28" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F28" s="168" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="G28" s="168" t="s">
         <v>47</v>
@@ -36652,19 +36570,19 @@
       <c r="B29" s="316"/>
       <c r="C29" s="345"/>
       <c r="D29" s="344" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E29" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F29" s="168" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="G29" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H29" s="255" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I29" s="274"/>
       <c r="J29" s="175" t="s">
@@ -36698,19 +36616,19 @@
       <c r="B30" s="316"/>
       <c r="C30" s="345"/>
       <c r="D30" s="344" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E30" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F30" s="168" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="G30" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H30" s="255" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="I30" s="274"/>
       <c r="J30" s="175" t="s">
@@ -36743,16 +36661,16 @@
       </c>
       <c r="B31" s="316"/>
       <c r="C31" s="345" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D31" s="344" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E31" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F31" s="168" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="G31" s="168" t="s">
         <v>47</v>
@@ -36792,13 +36710,13 @@
       <c r="B32" s="316"/>
       <c r="C32" s="345"/>
       <c r="D32" s="344" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E32" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F32" s="168" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="G32" s="168" t="s">
         <v>47</v>
@@ -36836,13 +36754,13 @@
       <c r="B33" s="316"/>
       <c r="C33" s="345"/>
       <c r="D33" s="344" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E33" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F33" s="168" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="G33" s="168" t="s">
         <v>47</v>
@@ -36880,13 +36798,13 @@
       <c r="B34" s="316"/>
       <c r="C34" s="345"/>
       <c r="D34" s="344" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E34" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F34" s="168" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="G34" s="168" t="s">
         <v>47</v>
@@ -36924,13 +36842,13 @@
       <c r="B35" s="316"/>
       <c r="C35" s="345"/>
       <c r="D35" s="344" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E35" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F35" s="168" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="G35" s="168" t="s">
         <v>47</v>
@@ -36968,13 +36886,13 @@
       <c r="B36" s="316"/>
       <c r="C36" s="345"/>
       <c r="D36" s="344" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E36" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F36" s="168" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="G36" s="168" t="s">
         <v>47</v>
@@ -37011,22 +36929,22 @@
       </c>
       <c r="B37" s="316"/>
       <c r="C37" s="345" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D37" s="344" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="E37" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F37" s="168" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="G37" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H37" s="248" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="I37" s="274"/>
       <c r="J37" s="175" t="s">
@@ -37060,19 +36978,19 @@
       <c r="B38" s="316"/>
       <c r="C38" s="345"/>
       <c r="D38" s="344" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E38" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F38" s="168" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="G38" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H38" s="248" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I38" s="274"/>
       <c r="J38" s="175" t="s">
@@ -37106,13 +37024,13 @@
       <c r="B39" s="316"/>
       <c r="C39" s="345"/>
       <c r="D39" s="344" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E39" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F39" s="168" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="G39" s="168" t="s">
         <v>47</v>
@@ -37149,22 +37067,22 @@
       </c>
       <c r="B40" s="316"/>
       <c r="C40" s="345" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D40" s="344" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E40" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F40" s="168" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="G40" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H40" s="248" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="I40" s="274"/>
       <c r="J40" s="175" t="s">
@@ -37198,19 +37116,19 @@
       <c r="B41" s="316"/>
       <c r="C41" s="345"/>
       <c r="D41" s="344" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="E41" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F41" s="168" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="G41" s="168" t="s">
         <v>47</v>
       </c>
       <c r="H41" s="248" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="I41" s="274"/>
       <c r="J41" s="175" t="s">
@@ -37244,13 +37162,13 @@
       <c r="B42" s="316"/>
       <c r="C42" s="345"/>
       <c r="D42" s="344" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E42" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F42" s="168" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="G42" s="168" t="s">
         <v>47</v>
@@ -37287,16 +37205,16 @@
       </c>
       <c r="B43" s="316"/>
       <c r="C43" s="345" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D43" s="344" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="E43" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F43" s="168" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="G43" s="168" t="s">
         <v>47</v>
@@ -37334,13 +37252,13 @@
       <c r="B44" s="316"/>
       <c r="C44" s="345"/>
       <c r="D44" s="344" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="E44" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F44" s="168" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="G44" s="168" t="s">
         <v>47</v>
@@ -37377,16 +37295,16 @@
       </c>
       <c r="B45" s="316"/>
       <c r="C45" s="345" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D45" s="344" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="E45" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F45" s="168" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="G45" s="168" t="s">
         <v>47</v>
@@ -37424,13 +37342,13 @@
       <c r="B46" s="316"/>
       <c r="C46" s="345"/>
       <c r="D46" s="344" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E46" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F46" s="168" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="G46" s="168" t="s">
         <v>47</v>
@@ -37468,13 +37386,13 @@
       <c r="B47" s="316"/>
       <c r="C47" s="345"/>
       <c r="D47" s="344" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E47" s="203" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F47" s="168" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="G47" s="168" t="s">
         <v>47</v>
@@ -37541,20 +37459,20 @@
       <c r="A49" s="61">
         <v>1</v>
       </c>
-      <c r="B49" s="435" t="s">
-        <v>166</v>
+      <c r="B49" s="433" t="s">
+        <v>158</v>
       </c>
       <c r="C49" s="202" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D49" s="168" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E49" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F49" s="203" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G49" s="203" t="s">
         <v>47</v>
@@ -37591,22 +37509,22 @@
       <c r="A50" s="61">
         <v>2</v>
       </c>
-      <c r="B50" s="435"/>
+      <c r="B50" s="433"/>
       <c r="C50" s="202"/>
       <c r="D50" s="168" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E50" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F50" s="203" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G50" s="203" t="s">
         <v>47</v>
       </c>
       <c r="H50" s="255" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I50" s="274"/>
       <c r="J50" s="175" t="s">
@@ -37637,22 +37555,22 @@
       <c r="A51" s="61">
         <v>3</v>
       </c>
-      <c r="B51" s="435"/>
+      <c r="B51" s="433"/>
       <c r="C51" s="202"/>
       <c r="D51" s="168" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E51" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F51" s="203" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G51" s="203" t="s">
         <v>47</v>
       </c>
       <c r="H51" s="255" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="I51" s="274"/>
       <c r="J51" s="175" t="s">
@@ -37683,22 +37601,22 @@
       <c r="A52" s="61">
         <v>4</v>
       </c>
-      <c r="B52" s="435"/>
+      <c r="B52" s="433"/>
       <c r="C52" s="202"/>
       <c r="D52" s="168" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E52" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F52" s="203" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G52" s="203" t="s">
         <v>47</v>
       </c>
       <c r="H52" s="256" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="I52" s="274"/>
       <c r="J52" s="175" t="s">
@@ -37729,22 +37647,22 @@
       <c r="A53" s="61">
         <v>5</v>
       </c>
-      <c r="B53" s="435"/>
+      <c r="B53" s="433"/>
       <c r="C53" s="202"/>
       <c r="D53" s="168" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E53" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F53" s="203" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G53" s="203" t="s">
         <v>47</v>
       </c>
       <c r="H53" s="256" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I53" s="274"/>
       <c r="J53" s="175" t="s">
@@ -37775,22 +37693,22 @@
       <c r="A54" s="61">
         <v>6</v>
       </c>
-      <c r="B54" s="435"/>
+      <c r="B54" s="433"/>
       <c r="C54" s="202"/>
       <c r="D54" s="168" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E54" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F54" s="203" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G54" s="203" t="s">
         <v>47</v>
       </c>
       <c r="H54" s="256" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I54" s="274"/>
       <c r="J54" s="175" t="s">
@@ -37821,22 +37739,22 @@
       <c r="A55" s="61">
         <v>7</v>
       </c>
-      <c r="B55" s="435"/>
+      <c r="B55" s="433"/>
       <c r="C55" s="202"/>
       <c r="D55" s="168" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E55" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F55" s="203" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="G55" s="203" t="s">
         <v>47</v>
       </c>
       <c r="H55" s="255" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="I55" s="274"/>
       <c r="J55" s="175" t="s">
@@ -37867,22 +37785,22 @@
       <c r="A56" s="61">
         <v>8</v>
       </c>
-      <c r="B56" s="435"/>
+      <c r="B56" s="433"/>
       <c r="C56" s="333"/>
       <c r="D56" s="168" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E56" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F56" s="203" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G56" s="203" t="s">
         <v>47</v>
       </c>
       <c r="H56" s="248" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I56" s="274"/>
       <c r="J56" s="175" t="s">
@@ -37913,22 +37831,22 @@
       <c r="A57" s="61">
         <v>9</v>
       </c>
-      <c r="B57" s="435"/>
+      <c r="B57" s="433"/>
       <c r="C57" s="333"/>
       <c r="D57" s="168" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E57" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F57" s="203" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G57" s="203" t="s">
         <v>47</v>
       </c>
       <c r="H57" s="248" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="I57" s="274"/>
       <c r="J57" s="175" t="s">
@@ -37959,22 +37877,22 @@
       <c r="A58" s="61">
         <v>10</v>
       </c>
-      <c r="B58" s="435"/>
+      <c r="B58" s="433"/>
       <c r="C58" s="333"/>
       <c r="D58" s="168" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E58" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F58" s="203" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="G58" s="203" t="s">
         <v>47</v>
       </c>
       <c r="H58" s="248" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I58" s="274"/>
       <c r="J58" s="175" t="s">
@@ -38005,28 +37923,28 @@
       <c r="A59" s="61">
         <v>11</v>
       </c>
-      <c r="B59" s="435"/>
+      <c r="B59" s="433"/>
       <c r="C59" s="333"/>
       <c r="D59" s="168" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E59" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F59" s="203" t="s">
+        <v>193</v>
+      </c>
+      <c r="G59" s="203" t="s">
+        <v>196</v>
+      </c>
+      <c r="H59" s="248" t="s">
+        <v>197</v>
+      </c>
+      <c r="I59" s="298" t="s">
         <v>201</v>
       </c>
-      <c r="G59" s="203" t="s">
-        <v>204</v>
-      </c>
-      <c r="H59" s="248" t="s">
-        <v>205</v>
-      </c>
-      <c r="I59" s="298" t="s">
-        <v>209</v>
-      </c>
       <c r="J59" s="175" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K59" s="65"/>
       <c r="L59" s="62"/>
@@ -38053,28 +37971,28 @@
       <c r="A60" s="61">
         <v>12</v>
       </c>
-      <c r="B60" s="435"/>
+      <c r="B60" s="433"/>
       <c r="C60" s="333"/>
       <c r="D60" s="168" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E60" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F60" s="203" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G60" s="203" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H60" s="296" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="I60" s="317" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="J60" s="297" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K60" s="65"/>
       <c r="L60" s="62"/>
@@ -38101,28 +38019,28 @@
       <c r="A61" s="179">
         <v>13</v>
       </c>
-      <c r="B61" s="435"/>
+      <c r="B61" s="433"/>
       <c r="C61" s="333"/>
       <c r="D61" s="168" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E61" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F61" s="203" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G61" s="203" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H61" s="257" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I61" s="351" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="J61" s="175" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K61" s="62"/>
       <c r="L61" s="66"/>
@@ -38149,28 +38067,28 @@
       <c r="A62" s="179">
         <v>14</v>
       </c>
-      <c r="B62" s="435"/>
+      <c r="B62" s="433"/>
       <c r="C62" s="333"/>
       <c r="D62" s="180" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E62" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F62" s="203" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G62" s="203" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H62" s="299" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I62" s="301" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="J62" s="297" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K62" s="61"/>
       <c r="L62" s="61"/>
@@ -38197,22 +38115,22 @@
       <c r="A63" s="179">
         <v>15</v>
       </c>
-      <c r="B63" s="435"/>
+      <c r="B63" s="433"/>
       <c r="C63" s="334"/>
       <c r="D63" s="318" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E63" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F63" s="203" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G63" s="203" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="H63" s="254" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="I63" s="300"/>
       <c r="J63" s="175" t="s">
@@ -38243,19 +38161,19 @@
       <c r="A64" s="179">
         <v>16</v>
       </c>
-      <c r="B64" s="436"/>
+      <c r="B64" s="434"/>
       <c r="C64" s="333"/>
       <c r="D64" s="303" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E64" s="203" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F64" s="203" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G64" s="203" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="H64" s="254" t="s">
         <v>49</v>
@@ -38321,21 +38239,21 @@
       <c r="A66" s="179">
         <v>1</v>
       </c>
-      <c r="B66" s="432" t="s">
-        <v>231</v>
+      <c r="B66" s="430" t="s">
+        <v>223</v>
       </c>
       <c r="C66" s="334"/>
       <c r="D66" s="304" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E66" s="239" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F66" s="203" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G66" s="203" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="H66" s="254" t="s">
         <v>49</v>
@@ -38369,19 +38287,19 @@
       <c r="A67" s="179">
         <v>2</v>
       </c>
-      <c r="B67" s="433"/>
+      <c r="B67" s="431"/>
       <c r="C67" s="333"/>
       <c r="D67" s="319" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E67" s="239" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F67" s="203" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G67" s="203" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="H67" s="254" t="s">
         <v>49</v>
@@ -38415,19 +38333,19 @@
       <c r="A68" s="179">
         <v>3</v>
       </c>
-      <c r="B68" s="434"/>
+      <c r="B68" s="432"/>
       <c r="C68" s="334"/>
       <c r="D68" s="318" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E68" s="239" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F68" s="56" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G68" s="203" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="H68" s="254" t="s">
         <v>49</v>
@@ -38492,7 +38410,7 @@
     <row r="70" spans="1:30" ht="16.5" thickBot="1">
       <c r="A70" s="179"/>
       <c r="B70" s="307" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C70" s="333"/>
       <c r="D70" s="319"/>
@@ -39135,7 +39053,7 @@
       <c r="A90" s="179"/>
       <c r="B90" s="307"/>
       <c r="C90" s="334"/>
-      <c r="D90" s="446"/>
+      <c r="D90" s="439"/>
       <c r="E90" s="362"/>
       <c r="F90" s="244"/>
       <c r="G90" s="216"/>
@@ -39167,7 +39085,7 @@
       <c r="A91" s="179"/>
       <c r="B91" s="307"/>
       <c r="C91" s="334"/>
-      <c r="D91" s="447"/>
+      <c r="D91" s="440"/>
       <c r="E91" s="363"/>
       <c r="F91" s="242"/>
       <c r="G91" s="30"/>
@@ -39231,7 +39149,7 @@
       <c r="A93" s="179"/>
       <c r="B93" s="307"/>
       <c r="C93" s="334"/>
-      <c r="D93" s="446"/>
+      <c r="D93" s="439"/>
       <c r="E93" s="365"/>
       <c r="F93" s="242"/>
       <c r="G93" s="30"/>
@@ -39263,7 +39181,7 @@
       <c r="A94" s="179"/>
       <c r="B94" s="307"/>
       <c r="C94" s="334"/>
-      <c r="D94" s="448"/>
+      <c r="D94" s="441"/>
       <c r="E94" s="366"/>
       <c r="F94" s="244"/>
       <c r="G94" s="30"/>
@@ -39295,7 +39213,7 @@
       <c r="A95" s="179"/>
       <c r="B95" s="307"/>
       <c r="C95" s="334"/>
-      <c r="D95" s="448"/>
+      <c r="D95" s="441"/>
       <c r="E95" s="366"/>
       <c r="F95" s="242"/>
       <c r="G95" s="30"/>
@@ -39327,7 +39245,7 @@
       <c r="A96" s="179"/>
       <c r="B96" s="307"/>
       <c r="C96" s="334"/>
-      <c r="D96" s="448"/>
+      <c r="D96" s="441"/>
       <c r="E96" s="366"/>
       <c r="F96" s="244"/>
       <c r="G96" s="216"/>
@@ -39359,7 +39277,7 @@
       <c r="A97" s="179"/>
       <c r="B97" s="307"/>
       <c r="C97" s="334"/>
-      <c r="D97" s="448"/>
+      <c r="D97" s="441"/>
       <c r="E97" s="366"/>
       <c r="F97" s="217"/>
       <c r="G97" s="228"/>
@@ -39391,7 +39309,7 @@
       <c r="A98" s="179"/>
       <c r="B98" s="307"/>
       <c r="C98" s="334"/>
-      <c r="D98" s="448"/>
+      <c r="D98" s="441"/>
       <c r="E98" s="366"/>
       <c r="F98" s="244"/>
       <c r="G98" s="215"/>
@@ -39423,7 +39341,7 @@
       <c r="A99" s="179"/>
       <c r="B99" s="307"/>
       <c r="C99" s="334"/>
-      <c r="D99" s="447"/>
+      <c r="D99" s="440"/>
       <c r="E99" s="363"/>
       <c r="F99" s="217"/>
       <c r="G99" s="229"/>
@@ -39487,7 +39405,7 @@
       <c r="A101" s="179"/>
       <c r="B101" s="307"/>
       <c r="C101" s="333"/>
-      <c r="D101" s="449"/>
+      <c r="D101" s="442"/>
       <c r="E101" s="368"/>
       <c r="F101" s="217"/>
       <c r="G101" s="217"/>
@@ -39519,7 +39437,7 @@
       <c r="A102" s="179"/>
       <c r="B102" s="307"/>
       <c r="C102" s="333"/>
-      <c r="D102" s="450"/>
+      <c r="D102" s="443"/>
       <c r="F102" s="215"/>
       <c r="G102" s="217"/>
       <c r="H102" s="261"/>
@@ -39550,7 +39468,7 @@
       <c r="A103" s="179"/>
       <c r="B103" s="307"/>
       <c r="C103" s="333"/>
-      <c r="D103" s="450"/>
+      <c r="D103" s="443"/>
       <c r="F103" s="218"/>
       <c r="G103" s="218"/>
       <c r="H103" s="262"/>
@@ -39581,7 +39499,7 @@
       <c r="A104" s="179"/>
       <c r="B104" s="307"/>
       <c r="C104" s="333"/>
-      <c r="D104" s="450"/>
+      <c r="D104" s="443"/>
       <c r="F104" s="218"/>
       <c r="G104" s="218"/>
       <c r="H104" s="262"/>
@@ -39612,7 +39530,7 @@
       <c r="A105" s="179"/>
       <c r="B105" s="307"/>
       <c r="C105" s="333"/>
-      <c r="D105" s="450"/>
+      <c r="D105" s="443"/>
       <c r="F105" s="218"/>
       <c r="G105" s="218"/>
       <c r="H105" s="262"/>
@@ -39643,7 +39561,7 @@
       <c r="A106" s="179"/>
       <c r="B106" s="307"/>
       <c r="C106" s="333"/>
-      <c r="D106" s="450"/>
+      <c r="D106" s="443"/>
       <c r="F106" s="218"/>
       <c r="G106" s="218"/>
       <c r="H106" s="262"/>
@@ -39674,7 +39592,7 @@
       <c r="A107" s="179"/>
       <c r="B107" s="307"/>
       <c r="C107" s="333"/>
-      <c r="D107" s="450"/>
+      <c r="D107" s="443"/>
       <c r="F107" s="218"/>
       <c r="G107" s="218"/>
       <c r="H107" s="262"/>
@@ -39705,7 +39623,7 @@
       <c r="A108" s="179"/>
       <c r="B108" s="307"/>
       <c r="C108" s="333"/>
-      <c r="D108" s="450"/>
+      <c r="D108" s="443"/>
       <c r="F108" s="218"/>
       <c r="G108" s="218"/>
       <c r="H108" s="262"/>
@@ -39736,7 +39654,7 @@
       <c r="A109" s="179"/>
       <c r="B109" s="307"/>
       <c r="C109" s="333"/>
-      <c r="D109" s="451"/>
+      <c r="D109" s="444"/>
       <c r="E109" s="370"/>
       <c r="F109" s="218"/>
       <c r="G109" s="218"/>
@@ -39864,7 +39782,7 @@
       <c r="A113" s="179"/>
       <c r="B113" s="307"/>
       <c r="C113" s="333"/>
-      <c r="D113" s="461"/>
+      <c r="D113" s="413"/>
       <c r="E113" s="373"/>
       <c r="F113" s="219"/>
       <c r="G113" s="218"/>
@@ -39896,7 +39814,7 @@
       <c r="A114" s="179"/>
       <c r="B114" s="307"/>
       <c r="C114" s="333"/>
-      <c r="D114" s="462"/>
+      <c r="D114" s="414"/>
       <c r="E114" s="374"/>
       <c r="F114" s="219"/>
       <c r="G114" s="218"/>
@@ -40920,7 +40838,7 @@
       <c r="A146" s="179"/>
       <c r="B146" s="307"/>
       <c r="C146" s="333"/>
-      <c r="D146" s="459"/>
+      <c r="D146" s="428"/>
       <c r="E146" s="379"/>
       <c r="F146" s="218"/>
       <c r="G146" s="218"/>
@@ -40930,7 +40848,7 @@
       <c r="K146" s="76"/>
       <c r="L146" s="76"/>
       <c r="M146" s="76"/>
-      <c r="N146" s="452"/>
+      <c r="N146" s="419"/>
       <c r="O146" s="70"/>
       <c r="P146" s="70"/>
       <c r="Q146" s="70"/>
@@ -40952,7 +40870,7 @@
       <c r="A147" s="179"/>
       <c r="B147" s="307"/>
       <c r="C147" s="333"/>
-      <c r="D147" s="460"/>
+      <c r="D147" s="429"/>
       <c r="E147" s="381"/>
       <c r="F147" s="218"/>
       <c r="G147" s="218"/>
@@ -40962,7 +40880,7 @@
       <c r="K147" s="76"/>
       <c r="L147" s="76"/>
       <c r="M147" s="76"/>
-      <c r="N147" s="453"/>
+      <c r="N147" s="421"/>
       <c r="O147" s="70"/>
       <c r="P147" s="70"/>
       <c r="Q147" s="70"/>
@@ -40984,7 +40902,7 @@
       <c r="A148" s="179"/>
       <c r="B148" s="307"/>
       <c r="C148" s="333"/>
-      <c r="D148" s="460"/>
+      <c r="D148" s="429"/>
       <c r="E148" s="381"/>
       <c r="F148" s="218"/>
       <c r="G148" s="218"/>
@@ -40994,7 +40912,7 @@
       <c r="K148" s="76"/>
       <c r="L148" s="76"/>
       <c r="M148" s="76"/>
-      <c r="N148" s="453"/>
+      <c r="N148" s="421"/>
       <c r="O148" s="70"/>
       <c r="P148" s="70"/>
       <c r="Q148" s="70"/>
@@ -41016,7 +40934,7 @@
       <c r="A149" s="179"/>
       <c r="B149" s="307"/>
       <c r="C149" s="333"/>
-      <c r="D149" s="460"/>
+      <c r="D149" s="429"/>
       <c r="E149" s="381"/>
       <c r="F149" s="221"/>
       <c r="G149" s="218"/>
@@ -41026,7 +40944,7 @@
       <c r="K149" s="76"/>
       <c r="L149" s="76"/>
       <c r="M149" s="76"/>
-      <c r="N149" s="453"/>
+      <c r="N149" s="421"/>
       <c r="O149" s="70"/>
       <c r="P149" s="70"/>
       <c r="Q149" s="70"/>
@@ -41048,7 +40966,7 @@
       <c r="A150" s="179"/>
       <c r="B150" s="307"/>
       <c r="C150" s="333"/>
-      <c r="D150" s="460"/>
+      <c r="D150" s="429"/>
       <c r="E150" s="381"/>
       <c r="F150" s="221"/>
       <c r="G150" s="218"/>
@@ -41058,7 +40976,7 @@
       <c r="K150" s="76"/>
       <c r="L150" s="76"/>
       <c r="M150" s="76"/>
-      <c r="N150" s="453"/>
+      <c r="N150" s="421"/>
       <c r="O150" s="70"/>
       <c r="P150" s="70"/>
       <c r="Q150" s="70"/>
@@ -41080,7 +40998,7 @@
       <c r="A151" s="179"/>
       <c r="B151" s="307"/>
       <c r="C151" s="333"/>
-      <c r="D151" s="460"/>
+      <c r="D151" s="429"/>
       <c r="E151" s="381"/>
       <c r="F151" s="221"/>
       <c r="G151" s="218"/>
@@ -41090,7 +41008,7 @@
       <c r="K151" s="76"/>
       <c r="L151" s="76"/>
       <c r="M151" s="76"/>
-      <c r="N151" s="453"/>
+      <c r="N151" s="421"/>
       <c r="O151" s="70"/>
       <c r="P151" s="70"/>
       <c r="Q151" s="70"/>
@@ -41112,7 +41030,7 @@
       <c r="A152" s="179"/>
       <c r="B152" s="307"/>
       <c r="C152" s="333"/>
-      <c r="D152" s="460"/>
+      <c r="D152" s="429"/>
       <c r="E152" s="381"/>
       <c r="F152" s="221"/>
       <c r="G152" s="218"/>
@@ -41122,7 +41040,7 @@
       <c r="K152" s="76"/>
       <c r="L152" s="76"/>
       <c r="M152" s="76"/>
-      <c r="N152" s="453"/>
+      <c r="N152" s="421"/>
       <c r="O152" s="70"/>
       <c r="P152" s="70"/>
       <c r="Q152" s="70"/>
@@ -41144,7 +41062,7 @@
       <c r="A153" s="179"/>
       <c r="B153" s="307"/>
       <c r="C153" s="333"/>
-      <c r="D153" s="460"/>
+      <c r="D153" s="429"/>
       <c r="E153" s="381"/>
       <c r="F153" s="218"/>
       <c r="G153" s="218"/>
@@ -41154,7 +41072,7 @@
       <c r="K153" s="76"/>
       <c r="L153" s="76"/>
       <c r="M153" s="76"/>
-      <c r="N153" s="454"/>
+      <c r="N153" s="416"/>
       <c r="O153" s="70"/>
       <c r="P153" s="70"/>
       <c r="Q153" s="70"/>
@@ -41176,7 +41094,7 @@
       <c r="A154" s="179"/>
       <c r="B154" s="307"/>
       <c r="C154" s="333"/>
-      <c r="D154" s="460"/>
+      <c r="D154" s="429"/>
       <c r="E154" s="381"/>
       <c r="F154" s="218"/>
       <c r="G154" s="218"/>
@@ -41208,7 +41126,7 @@
       <c r="A155" s="179"/>
       <c r="B155" s="307"/>
       <c r="C155" s="335"/>
-      <c r="D155" s="460"/>
+      <c r="D155" s="429"/>
       <c r="E155" s="381"/>
       <c r="F155" s="218"/>
       <c r="G155" s="218"/>
@@ -41242,7 +41160,7 @@
       <c r="C156" s="336" t="s">
         <v>51</v>
       </c>
-      <c r="D156" s="460"/>
+      <c r="D156" s="429"/>
       <c r="E156" s="381"/>
       <c r="F156" s="218"/>
       <c r="G156" s="218"/>
@@ -41306,7 +41224,7 @@
       <c r="A158" s="186"/>
       <c r="B158" s="309"/>
       <c r="C158" s="337"/>
-      <c r="D158" s="456"/>
+      <c r="D158" s="425"/>
       <c r="E158" s="223"/>
       <c r="F158" s="218"/>
       <c r="G158" s="218"/>
@@ -41338,7 +41256,7 @@
       <c r="A159" s="186"/>
       <c r="B159" s="310"/>
       <c r="C159" s="336"/>
-      <c r="D159" s="457"/>
+      <c r="D159" s="426"/>
       <c r="E159" s="383"/>
       <c r="F159" s="218"/>
       <c r="G159" s="218"/>
@@ -41370,7 +41288,7 @@
       <c r="A160" s="186"/>
       <c r="B160" s="310"/>
       <c r="C160" s="336"/>
-      <c r="D160" s="457"/>
+      <c r="D160" s="426"/>
       <c r="E160" s="383"/>
       <c r="F160" s="218"/>
       <c r="G160" s="218"/>
@@ -41402,7 +41320,7 @@
       <c r="A161" s="186"/>
       <c r="B161" s="310"/>
       <c r="C161" s="336"/>
-      <c r="D161" s="457"/>
+      <c r="D161" s="426"/>
       <c r="E161" s="383"/>
       <c r="F161" s="218"/>
       <c r="G161" s="218"/>
@@ -41434,7 +41352,7 @@
       <c r="A162" s="186"/>
       <c r="B162" s="309"/>
       <c r="C162" s="336"/>
-      <c r="D162" s="457"/>
+      <c r="D162" s="426"/>
       <c r="E162" s="383"/>
       <c r="F162" s="218"/>
       <c r="G162" s="218"/>
@@ -41466,7 +41384,7 @@
       <c r="A163" s="186"/>
       <c r="B163" s="309"/>
       <c r="C163" s="336"/>
-      <c r="D163" s="457"/>
+      <c r="D163" s="426"/>
       <c r="E163" s="383"/>
       <c r="F163" s="218"/>
       <c r="G163" s="218"/>
@@ -41498,7 +41416,7 @@
       <c r="A164" s="186"/>
       <c r="B164" s="309"/>
       <c r="C164" s="336"/>
-      <c r="D164" s="457"/>
+      <c r="D164" s="426"/>
       <c r="E164" s="383"/>
       <c r="F164" s="218"/>
       <c r="G164" s="218"/>
@@ -41530,7 +41448,7 @@
       <c r="A165" s="186"/>
       <c r="B165" s="309"/>
       <c r="C165" s="336"/>
-      <c r="D165" s="457"/>
+      <c r="D165" s="426"/>
       <c r="E165" s="383"/>
       <c r="F165" s="218"/>
       <c r="G165" s="218"/>
@@ -41562,7 +41480,7 @@
       <c r="A166" s="186"/>
       <c r="B166" s="309"/>
       <c r="C166" s="336"/>
-      <c r="D166" s="458"/>
+      <c r="D166" s="427"/>
       <c r="E166" s="384"/>
       <c r="F166" s="218"/>
       <c r="G166" s="218"/>
@@ -42916,7 +42834,7 @@
       <c r="I208" s="282"/>
       <c r="J208" s="87"/>
       <c r="K208" s="72"/>
-      <c r="L208" s="452"/>
+      <c r="L208" s="419"/>
       <c r="M208" s="76"/>
       <c r="N208" s="187"/>
       <c r="O208" s="70"/>
@@ -42948,8 +42866,8 @@
       <c r="I209" s="289"/>
       <c r="J209" s="90"/>
       <c r="K209" s="86"/>
-      <c r="L209" s="453"/>
-      <c r="M209" s="452"/>
+      <c r="L209" s="421"/>
+      <c r="M209" s="419"/>
       <c r="N209" s="187"/>
       <c r="O209" s="70"/>
       <c r="P209" s="70"/>
@@ -42980,8 +42898,8 @@
       <c r="I210" s="290"/>
       <c r="J210" s="69"/>
       <c r="K210" s="89"/>
-      <c r="L210" s="454"/>
-      <c r="M210" s="453"/>
+      <c r="L210" s="416"/>
+      <c r="M210" s="421"/>
       <c r="N210" s="187"/>
       <c r="O210" s="70"/>
       <c r="P210" s="70"/>
@@ -43013,7 +42931,7 @@
       <c r="J211" s="87"/>
       <c r="K211" s="68"/>
       <c r="L211" s="81"/>
-      <c r="M211" s="454"/>
+      <c r="M211" s="416"/>
       <c r="N211" s="187"/>
       <c r="O211" s="70"/>
       <c r="P211" s="70"/>
@@ -43163,7 +43081,7 @@
     <row r="216" spans="1:30">
       <c r="A216" s="186"/>
       <c r="B216" s="309"/>
-      <c r="C216" s="437"/>
+      <c r="C216" s="417"/>
       <c r="D216" s="234"/>
       <c r="E216" s="223"/>
       <c r="F216" s="30"/>
@@ -43195,7 +43113,7 @@
     <row r="217" spans="1:30">
       <c r="A217" s="186"/>
       <c r="B217" s="309"/>
-      <c r="C217" s="438"/>
+      <c r="C217" s="420"/>
       <c r="D217" s="234"/>
       <c r="E217" s="223"/>
       <c r="F217" s="30"/>
@@ -43227,10 +43145,10 @@
     <row r="218" spans="1:30">
       <c r="A218" s="186"/>
       <c r="B218" s="309"/>
-      <c r="C218" s="438"/>
+      <c r="C218" s="420"/>
       <c r="D218" s="235"/>
       <c r="E218" s="220"/>
-      <c r="F218" s="455"/>
+      <c r="F218" s="422"/>
       <c r="G218" s="30"/>
       <c r="H218" s="260"/>
       <c r="I218" s="282"/>
@@ -43259,10 +43177,10 @@
     <row r="219" spans="1:30">
       <c r="A219" s="186"/>
       <c r="B219" s="309"/>
-      <c r="C219" s="438"/>
+      <c r="C219" s="420"/>
       <c r="D219" s="235"/>
       <c r="E219" s="223"/>
-      <c r="F219" s="441"/>
+      <c r="F219" s="423"/>
       <c r="G219" s="30"/>
       <c r="H219" s="260"/>
       <c r="I219" s="282"/>
@@ -43291,10 +43209,10 @@
     <row r="220" spans="1:30">
       <c r="A220" s="186"/>
       <c r="B220" s="309"/>
-      <c r="C220" s="438"/>
+      <c r="C220" s="420"/>
       <c r="D220" s="235"/>
       <c r="E220" s="221"/>
-      <c r="F220" s="442"/>
+      <c r="F220" s="424"/>
       <c r="G220" s="30"/>
       <c r="H220" s="260"/>
       <c r="I220" s="282"/>
@@ -43323,7 +43241,7 @@
     <row r="221" spans="1:30">
       <c r="A221" s="186"/>
       <c r="B221" s="309"/>
-      <c r="C221" s="438"/>
+      <c r="C221" s="420"/>
       <c r="D221" s="235"/>
       <c r="E221" s="218"/>
       <c r="F221" s="30"/>
@@ -43355,7 +43273,7 @@
     <row r="222" spans="1:30">
       <c r="A222" s="186"/>
       <c r="B222" s="309"/>
-      <c r="C222" s="439"/>
+      <c r="C222" s="418"/>
       <c r="D222" s="235"/>
       <c r="E222" s="218"/>
       <c r="F222" s="30"/>
@@ -43387,7 +43305,7 @@
     <row r="223" spans="1:30">
       <c r="A223" s="186"/>
       <c r="B223" s="309"/>
-      <c r="C223" s="437"/>
+      <c r="C223" s="417"/>
       <c r="D223" s="235"/>
       <c r="E223" s="218"/>
       <c r="F223" s="30"/>
@@ -43419,7 +43337,7 @@
     <row r="224" spans="1:30">
       <c r="A224" s="186"/>
       <c r="B224" s="309"/>
-      <c r="C224" s="439"/>
+      <c r="C224" s="418"/>
       <c r="D224" s="235"/>
       <c r="E224" s="218"/>
       <c r="F224" s="30"/>
@@ -43483,7 +43401,7 @@
     <row r="226" spans="1:30">
       <c r="A226" s="186"/>
       <c r="B226" s="309"/>
-      <c r="C226" s="437"/>
+      <c r="C226" s="417"/>
       <c r="D226" s="236"/>
       <c r="E226" s="221"/>
       <c r="F226" s="30"/>
@@ -43515,7 +43433,7 @@
     <row r="227" spans="1:30">
       <c r="A227" s="186"/>
       <c r="B227" s="309"/>
-      <c r="C227" s="438"/>
+      <c r="C227" s="420"/>
       <c r="D227" s="235"/>
       <c r="E227" s="218"/>
       <c r="F227" s="30"/>
@@ -43547,7 +43465,7 @@
     <row r="228" spans="1:30">
       <c r="A228" s="186"/>
       <c r="B228" s="309"/>
-      <c r="C228" s="438"/>
+      <c r="C228" s="420"/>
       <c r="D228" s="237"/>
       <c r="E228" s="220"/>
       <c r="F228" s="30"/>
@@ -43579,7 +43497,7 @@
     <row r="229" spans="1:30">
       <c r="A229" s="186"/>
       <c r="B229" s="309"/>
-      <c r="C229" s="438"/>
+      <c r="C229" s="420"/>
       <c r="D229" s="234"/>
       <c r="E229" s="223"/>
       <c r="F229" s="30"/>
@@ -43611,7 +43529,7 @@
     <row r="230" spans="1:30">
       <c r="A230" s="186"/>
       <c r="B230" s="309"/>
-      <c r="C230" s="439"/>
+      <c r="C230" s="418"/>
       <c r="D230" s="234"/>
       <c r="E230" s="223"/>
       <c r="F230" s="30"/>
@@ -44036,7 +43954,7 @@
       <c r="I243" s="282"/>
       <c r="J243" s="73"/>
       <c r="K243" s="72"/>
-      <c r="L243" s="463"/>
+      <c r="L243" s="415"/>
       <c r="M243" s="76"/>
       <c r="N243" s="94"/>
       <c r="O243" s="70"/>
@@ -44068,7 +43986,7 @@
       <c r="I244" s="282"/>
       <c r="J244" s="73"/>
       <c r="K244" s="72"/>
-      <c r="L244" s="454"/>
+      <c r="L244" s="416"/>
       <c r="M244" s="76"/>
       <c r="N244" s="94"/>
       <c r="O244" s="70"/>
@@ -44123,7 +44041,7 @@
     <row r="246" spans="1:30">
       <c r="A246" s="186"/>
       <c r="B246" s="309"/>
-      <c r="C246" s="437"/>
+      <c r="C246" s="417"/>
       <c r="D246" s="235"/>
       <c r="E246" s="218"/>
       <c r="F246" s="30"/>
@@ -44155,7 +44073,7 @@
     <row r="247" spans="1:30">
       <c r="A247" s="186"/>
       <c r="B247" s="309"/>
-      <c r="C247" s="439"/>
+      <c r="C247" s="418"/>
       <c r="D247" s="235"/>
       <c r="E247" s="218"/>
       <c r="F247" s="30"/>
@@ -44164,7 +44082,7 @@
       <c r="I247" s="281"/>
       <c r="J247" s="73"/>
       <c r="K247" s="68"/>
-      <c r="L247" s="452"/>
+      <c r="L247" s="419"/>
       <c r="M247" s="91"/>
       <c r="N247" s="94"/>
       <c r="O247" s="70"/>
@@ -44187,7 +44105,7 @@
     <row r="248" spans="1:30">
       <c r="A248" s="186"/>
       <c r="B248" s="309"/>
-      <c r="C248" s="437"/>
+      <c r="C248" s="417"/>
       <c r="D248" s="237"/>
       <c r="E248" s="220"/>
       <c r="F248" s="30"/>
@@ -44196,7 +44114,7 @@
       <c r="I248" s="282"/>
       <c r="J248" s="73"/>
       <c r="K248" s="72"/>
-      <c r="L248" s="454"/>
+      <c r="L248" s="416"/>
       <c r="M248" s="76"/>
       <c r="N248" s="94"/>
       <c r="O248" s="70"/>
@@ -44219,7 +44137,7 @@
     <row r="249" spans="1:30">
       <c r="A249" s="186"/>
       <c r="B249" s="309"/>
-      <c r="C249" s="439"/>
+      <c r="C249" s="418"/>
       <c r="D249" s="236"/>
       <c r="E249" s="221"/>
       <c r="F249" s="30"/>
@@ -44283,7 +44201,7 @@
     <row r="251" spans="1:30">
       <c r="A251" s="186"/>
       <c r="B251" s="309"/>
-      <c r="C251" s="437"/>
+      <c r="C251" s="417"/>
       <c r="D251" s="236"/>
       <c r="E251" s="221"/>
       <c r="F251" s="218"/>
@@ -44315,7 +44233,7 @@
     <row r="252" spans="1:30">
       <c r="A252" s="186"/>
       <c r="B252" s="309"/>
-      <c r="C252" s="438"/>
+      <c r="C252" s="420"/>
       <c r="D252" s="235"/>
       <c r="E252" s="218"/>
       <c r="F252" s="218"/>
@@ -44347,7 +44265,7 @@
     <row r="253" spans="1:30">
       <c r="A253" s="186"/>
       <c r="B253" s="309"/>
-      <c r="C253" s="439"/>
+      <c r="C253" s="418"/>
       <c r="D253" s="237"/>
       <c r="E253" s="220"/>
       <c r="F253" s="218"/>
@@ -44539,7 +44457,7 @@
     <row r="259" spans="1:30">
       <c r="A259" s="191"/>
       <c r="B259" s="313"/>
-      <c r="C259" s="437"/>
+      <c r="C259" s="417"/>
       <c r="D259" s="234"/>
       <c r="E259" s="223"/>
       <c r="F259" s="218"/>
@@ -44571,7 +44489,7 @@
     <row r="260" spans="1:30">
       <c r="A260" s="191"/>
       <c r="B260" s="313"/>
-      <c r="C260" s="438"/>
+      <c r="C260" s="420"/>
       <c r="D260" s="234"/>
       <c r="E260" s="223"/>
       <c r="F260" s="218"/>
@@ -44602,11 +44520,11 @@
     </row>
     <row r="261" spans="1:30">
       <c r="A261" s="191"/>
-      <c r="B261" s="443"/>
-      <c r="C261" s="438"/>
+      <c r="B261" s="436"/>
+      <c r="C261" s="420"/>
       <c r="D261" s="235"/>
       <c r="E261" s="220"/>
-      <c r="F261" s="440"/>
+      <c r="F261" s="435"/>
       <c r="G261" s="30"/>
       <c r="H261" s="260"/>
       <c r="I261" s="282"/>
@@ -44634,11 +44552,11 @@
     </row>
     <row r="262" spans="1:30">
       <c r="A262" s="191"/>
-      <c r="B262" s="444"/>
-      <c r="C262" s="438"/>
+      <c r="B262" s="437"/>
+      <c r="C262" s="420"/>
       <c r="D262" s="235"/>
       <c r="E262" s="223"/>
-      <c r="F262" s="441"/>
+      <c r="F262" s="423"/>
       <c r="G262" s="30"/>
       <c r="H262" s="260"/>
       <c r="I262" s="282"/>
@@ -44666,11 +44584,11 @@
     </row>
     <row r="263" spans="1:30">
       <c r="A263" s="191"/>
-      <c r="B263" s="444"/>
-      <c r="C263" s="438"/>
+      <c r="B263" s="437"/>
+      <c r="C263" s="420"/>
       <c r="D263" s="235"/>
       <c r="E263" s="223"/>
-      <c r="F263" s="441"/>
+      <c r="F263" s="423"/>
       <c r="G263" s="30"/>
       <c r="H263" s="260"/>
       <c r="I263" s="282"/>
@@ -44698,11 +44616,11 @@
     </row>
     <row r="264" spans="1:30">
       <c r="A264" s="191"/>
-      <c r="B264" s="444"/>
-      <c r="C264" s="438"/>
+      <c r="B264" s="437"/>
+      <c r="C264" s="420"/>
       <c r="D264" s="235"/>
       <c r="E264" s="223"/>
-      <c r="F264" s="441"/>
+      <c r="F264" s="423"/>
       <c r="G264" s="30"/>
       <c r="H264" s="260"/>
       <c r="I264" s="282"/>
@@ -44730,11 +44648,11 @@
     </row>
     <row r="265" spans="1:30">
       <c r="A265" s="191"/>
-      <c r="B265" s="444"/>
-      <c r="C265" s="438"/>
+      <c r="B265" s="437"/>
+      <c r="C265" s="420"/>
       <c r="D265" s="235"/>
       <c r="E265" s="223"/>
-      <c r="F265" s="441"/>
+      <c r="F265" s="423"/>
       <c r="G265" s="30"/>
       <c r="H265" s="260"/>
       <c r="I265" s="282"/>
@@ -44762,11 +44680,11 @@
     </row>
     <row r="266" spans="1:30">
       <c r="A266" s="191"/>
-      <c r="B266" s="444"/>
-      <c r="C266" s="438"/>
+      <c r="B266" s="437"/>
+      <c r="C266" s="420"/>
       <c r="D266" s="235"/>
       <c r="E266" s="223"/>
-      <c r="F266" s="441"/>
+      <c r="F266" s="423"/>
       <c r="G266" s="30"/>
       <c r="H266" s="260"/>
       <c r="I266" s="282"/>
@@ -44794,11 +44712,11 @@
     </row>
     <row r="267" spans="1:30">
       <c r="A267" s="191"/>
-      <c r="B267" s="444"/>
-      <c r="C267" s="438"/>
+      <c r="B267" s="437"/>
+      <c r="C267" s="420"/>
       <c r="D267" s="235"/>
       <c r="E267" s="223"/>
-      <c r="F267" s="441"/>
+      <c r="F267" s="423"/>
       <c r="G267" s="30"/>
       <c r="H267" s="260"/>
       <c r="I267" s="282"/>
@@ -44826,11 +44744,11 @@
     </row>
     <row r="268" spans="1:30">
       <c r="A268" s="191"/>
-      <c r="B268" s="444"/>
-      <c r="C268" s="438"/>
+      <c r="B268" s="437"/>
+      <c r="C268" s="420"/>
       <c r="D268" s="235"/>
       <c r="E268" s="221"/>
-      <c r="F268" s="442"/>
+      <c r="F268" s="424"/>
       <c r="G268" s="30"/>
       <c r="H268" s="260"/>
       <c r="I268" s="282"/>
@@ -44858,8 +44776,8 @@
     </row>
     <row r="269" spans="1:30">
       <c r="A269" s="191"/>
-      <c r="B269" s="444"/>
-      <c r="C269" s="438"/>
+      <c r="B269" s="437"/>
+      <c r="C269" s="420"/>
       <c r="D269" s="235"/>
       <c r="E269" s="218"/>
       <c r="F269" s="218"/>
@@ -44890,8 +44808,8 @@
     </row>
     <row r="270" spans="1:30">
       <c r="A270" s="191"/>
-      <c r="B270" s="444"/>
-      <c r="C270" s="438"/>
+      <c r="B270" s="437"/>
+      <c r="C270" s="420"/>
       <c r="D270" s="235"/>
       <c r="E270" s="218"/>
       <c r="F270" s="218"/>
@@ -44922,11 +44840,11 @@
     </row>
     <row r="271" spans="1:30">
       <c r="A271" s="191"/>
-      <c r="B271" s="444"/>
-      <c r="C271" s="438"/>
+      <c r="B271" s="437"/>
+      <c r="C271" s="420"/>
       <c r="D271" s="237"/>
       <c r="E271" s="220"/>
-      <c r="F271" s="440"/>
+      <c r="F271" s="435"/>
       <c r="G271" s="218"/>
       <c r="H271" s="262"/>
       <c r="I271" s="284"/>
@@ -44954,11 +44872,11 @@
     </row>
     <row r="272" spans="1:30">
       <c r="A272" s="191"/>
-      <c r="B272" s="444"/>
-      <c r="C272" s="439"/>
+      <c r="B272" s="437"/>
+      <c r="C272" s="418"/>
       <c r="D272" s="234"/>
       <c r="E272" s="223"/>
-      <c r="F272" s="441"/>
+      <c r="F272" s="423"/>
       <c r="G272" s="218"/>
       <c r="H272" s="262"/>
       <c r="I272" s="284"/>
@@ -44986,11 +44904,11 @@
     </row>
     <row r="273" spans="1:30">
       <c r="A273" s="191"/>
-      <c r="B273" s="444"/>
+      <c r="B273" s="437"/>
       <c r="C273" s="336"/>
       <c r="D273" s="234"/>
       <c r="E273" s="223"/>
-      <c r="F273" s="441"/>
+      <c r="F273" s="423"/>
       <c r="G273" s="218"/>
       <c r="H273" s="262"/>
       <c r="I273" s="284"/>
@@ -45018,11 +44936,11 @@
     </row>
     <row r="274" spans="1:30">
       <c r="A274" s="191"/>
-      <c r="B274" s="444"/>
-      <c r="C274" s="437"/>
+      <c r="B274" s="437"/>
+      <c r="C274" s="417"/>
       <c r="D274" s="236"/>
       <c r="E274" s="221"/>
-      <c r="F274" s="442"/>
+      <c r="F274" s="424"/>
       <c r="G274" s="218"/>
       <c r="H274" s="262"/>
       <c r="I274" s="284"/>
@@ -45050,8 +44968,8 @@
     </row>
     <row r="275" spans="1:30">
       <c r="A275" s="191"/>
-      <c r="B275" s="444"/>
-      <c r="C275" s="438"/>
+      <c r="B275" s="437"/>
+      <c r="C275" s="420"/>
       <c r="D275" s="234"/>
       <c r="E275" s="223"/>
       <c r="F275" s="223"/>
@@ -45082,11 +45000,11 @@
     </row>
     <row r="276" spans="1:30">
       <c r="A276" s="191"/>
-      <c r="B276" s="444"/>
-      <c r="C276" s="438"/>
+      <c r="B276" s="437"/>
+      <c r="C276" s="420"/>
       <c r="D276" s="237"/>
       <c r="E276" s="220"/>
-      <c r="F276" s="440"/>
+      <c r="F276" s="435"/>
       <c r="G276" s="218"/>
       <c r="H276" s="262"/>
       <c r="I276" s="284"/>
@@ -45114,11 +45032,11 @@
     </row>
     <row r="277" spans="1:30">
       <c r="A277" s="191"/>
-      <c r="B277" s="444"/>
-      <c r="C277" s="439"/>
+      <c r="B277" s="437"/>
+      <c r="C277" s="418"/>
       <c r="D277" s="236"/>
       <c r="E277" s="221"/>
-      <c r="F277" s="442"/>
+      <c r="F277" s="424"/>
       <c r="G277" s="218"/>
       <c r="H277" s="262"/>
       <c r="I277" s="284"/>
@@ -45146,11 +45064,11 @@
     </row>
     <row r="278" spans="1:30">
       <c r="A278" s="191"/>
-      <c r="B278" s="444"/>
+      <c r="B278" s="437"/>
       <c r="C278" s="336"/>
       <c r="D278" s="235"/>
       <c r="E278" s="220"/>
-      <c r="F278" s="440"/>
+      <c r="F278" s="435"/>
       <c r="G278" s="218"/>
       <c r="H278" s="262"/>
       <c r="I278" s="284"/>
@@ -45178,11 +45096,11 @@
     </row>
     <row r="279" spans="1:30">
       <c r="A279" s="191"/>
-      <c r="B279" s="444"/>
-      <c r="C279" s="437"/>
+      <c r="B279" s="437"/>
+      <c r="C279" s="417"/>
       <c r="D279" s="235"/>
       <c r="E279" s="221"/>
-      <c r="F279" s="442"/>
+      <c r="F279" s="424"/>
       <c r="G279" s="218"/>
       <c r="H279" s="262"/>
       <c r="I279" s="284"/>
@@ -45210,8 +45128,8 @@
     </row>
     <row r="280" spans="1:30">
       <c r="A280" s="191"/>
-      <c r="B280" s="444"/>
-      <c r="C280" s="438"/>
+      <c r="B280" s="437"/>
+      <c r="C280" s="420"/>
       <c r="D280" s="235"/>
       <c r="E280" s="218"/>
       <c r="F280" s="218"/>
@@ -45242,11 +45160,11 @@
     </row>
     <row r="281" spans="1:30">
       <c r="A281" s="191"/>
-      <c r="B281" s="444"/>
-      <c r="C281" s="438"/>
+      <c r="B281" s="437"/>
+      <c r="C281" s="420"/>
       <c r="D281" s="237"/>
       <c r="E281" s="220"/>
-      <c r="F281" s="440"/>
+      <c r="F281" s="435"/>
       <c r="G281" s="218"/>
       <c r="H281" s="262"/>
       <c r="I281" s="284"/>
@@ -45274,11 +45192,11 @@
     </row>
     <row r="282" spans="1:30">
       <c r="A282" s="191"/>
-      <c r="B282" s="444"/>
-      <c r="C282" s="438"/>
+      <c r="B282" s="437"/>
+      <c r="C282" s="420"/>
       <c r="D282" s="234"/>
       <c r="E282" s="223"/>
-      <c r="F282" s="441"/>
+      <c r="F282" s="423"/>
       <c r="G282" s="218"/>
       <c r="H282" s="262"/>
       <c r="I282" s="284"/>
@@ -45306,11 +45224,11 @@
     </row>
     <row r="283" spans="1:30">
       <c r="A283" s="191"/>
-      <c r="B283" s="444"/>
-      <c r="C283" s="438"/>
+      <c r="B283" s="437"/>
+      <c r="C283" s="420"/>
       <c r="D283" s="234"/>
       <c r="E283" s="223"/>
-      <c r="F283" s="441"/>
+      <c r="F283" s="423"/>
       <c r="G283" s="218"/>
       <c r="H283" s="262"/>
       <c r="I283" s="284"/>
@@ -45338,11 +45256,11 @@
     </row>
     <row r="284" spans="1:30">
       <c r="A284" s="191"/>
-      <c r="B284" s="444"/>
-      <c r="C284" s="438"/>
+      <c r="B284" s="437"/>
+      <c r="C284" s="420"/>
       <c r="D284" s="234"/>
       <c r="E284" s="223"/>
-      <c r="F284" s="441"/>
+      <c r="F284" s="423"/>
       <c r="G284" s="218"/>
       <c r="H284" s="262"/>
       <c r="I284" s="284"/>
@@ -45370,11 +45288,11 @@
     </row>
     <row r="285" spans="1:30">
       <c r="A285" s="191"/>
-      <c r="B285" s="444"/>
-      <c r="C285" s="438"/>
+      <c r="B285" s="437"/>
+      <c r="C285" s="420"/>
       <c r="D285" s="234"/>
       <c r="E285" s="223"/>
-      <c r="F285" s="441"/>
+      <c r="F285" s="423"/>
       <c r="G285" s="30"/>
       <c r="H285" s="260"/>
       <c r="I285" s="282"/>
@@ -45402,11 +45320,11 @@
     </row>
     <row r="286" spans="1:30">
       <c r="A286" s="191"/>
-      <c r="B286" s="444"/>
-      <c r="C286" s="438"/>
+      <c r="B286" s="437"/>
+      <c r="C286" s="420"/>
       <c r="D286" s="236"/>
       <c r="E286" s="221"/>
-      <c r="F286" s="442"/>
+      <c r="F286" s="424"/>
       <c r="G286" s="30"/>
       <c r="H286" s="260"/>
       <c r="I286" s="282"/>
@@ -45434,11 +45352,11 @@
     </row>
     <row r="287" spans="1:30">
       <c r="A287" s="191"/>
-      <c r="B287" s="444"/>
-      <c r="C287" s="438"/>
+      <c r="B287" s="437"/>
+      <c r="C287" s="420"/>
       <c r="D287" s="237"/>
       <c r="E287" s="220"/>
-      <c r="F287" s="440"/>
+      <c r="F287" s="435"/>
       <c r="G287" s="218"/>
       <c r="H287" s="262"/>
       <c r="I287" s="284"/>
@@ -45466,11 +45384,11 @@
     </row>
     <row r="288" spans="1:30">
       <c r="A288" s="191"/>
-      <c r="B288" s="444"/>
-      <c r="C288" s="439"/>
+      <c r="B288" s="437"/>
+      <c r="C288" s="418"/>
       <c r="D288" s="234"/>
       <c r="E288" s="223"/>
-      <c r="F288" s="441"/>
+      <c r="F288" s="423"/>
       <c r="G288" s="218"/>
       <c r="H288" s="262"/>
       <c r="I288" s="284"/>
@@ -45498,11 +45416,11 @@
     </row>
     <row r="289" spans="1:30">
       <c r="A289" s="191"/>
-      <c r="B289" s="444"/>
+      <c r="B289" s="437"/>
       <c r="C289" s="336"/>
       <c r="D289" s="234"/>
       <c r="E289" s="223"/>
-      <c r="F289" s="441"/>
+      <c r="F289" s="423"/>
       <c r="G289" s="218"/>
       <c r="H289" s="262"/>
       <c r="I289" s="284"/>
@@ -45530,11 +45448,11 @@
     </row>
     <row r="290" spans="1:30">
       <c r="A290" s="191"/>
-      <c r="B290" s="445"/>
+      <c r="B290" s="438"/>
       <c r="C290" s="336"/>
       <c r="D290" s="236"/>
       <c r="E290" s="221"/>
-      <c r="F290" s="442"/>
+      <c r="F290" s="424"/>
       <c r="G290" s="218"/>
       <c r="H290" s="262"/>
       <c r="I290" s="284"/>
@@ -54499,20 +54417,18 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="D113:D114"/>
-    <mergeCell ref="L243:L244"/>
-    <mergeCell ref="C246:C247"/>
-    <mergeCell ref="L247:L248"/>
-    <mergeCell ref="C248:C249"/>
-    <mergeCell ref="C223:C224"/>
-    <mergeCell ref="C226:C230"/>
-    <mergeCell ref="N146:N153"/>
-    <mergeCell ref="L208:L210"/>
-    <mergeCell ref="M209:M211"/>
-    <mergeCell ref="C216:C222"/>
-    <mergeCell ref="F218:F220"/>
-    <mergeCell ref="D158:D166"/>
-    <mergeCell ref="D146:D156"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C18:C23"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="B8:B26"/>
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="B49:B64"/>
     <mergeCell ref="C251:C253"/>
@@ -54529,18 +54445,20 @@
     <mergeCell ref="D90:D91"/>
     <mergeCell ref="D93:D99"/>
     <mergeCell ref="D101:D109"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C18:C23"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="B8:B26"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="N146:N153"/>
+    <mergeCell ref="L208:L210"/>
+    <mergeCell ref="M209:M211"/>
+    <mergeCell ref="C216:C222"/>
+    <mergeCell ref="F218:F220"/>
+    <mergeCell ref="D158:D166"/>
+    <mergeCell ref="D146:D156"/>
+    <mergeCell ref="D113:D114"/>
+    <mergeCell ref="L243:L244"/>
+    <mergeCell ref="C246:C247"/>
+    <mergeCell ref="L247:L248"/>
+    <mergeCell ref="C248:C249"/>
+    <mergeCell ref="C223:C224"/>
+    <mergeCell ref="C226:C230"/>
   </mergeCells>
   <conditionalFormatting sqref="J8:J69 L20:L23 M24:M63">
     <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
@@ -54619,14 +54537,14 @@
     <row r="2" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="3" spans="1:26" ht="8.25" customHeight="1"/>
     <row r="4" spans="1:26" ht="25.5" customHeight="1">
-      <c r="B4" s="464" t="s">
+      <c r="B4" s="492" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="465"/>
-      <c r="D4" s="465"/>
-      <c r="E4" s="465"/>
-      <c r="F4" s="465"/>
-      <c r="G4" s="466"/>
+      <c r="C4" s="485"/>
+      <c r="D4" s="485"/>
+      <c r="E4" s="485"/>
+      <c r="F4" s="485"/>
+      <c r="G4" s="486"/>
       <c r="J4" s="97" t="s">
         <v>54</v>
       </c>
@@ -54636,25 +54554,25 @@
       <c r="B5" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="467" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" s="468"/>
-      <c r="E5" s="468"/>
-      <c r="F5" s="468"/>
-      <c r="G5" s="469"/>
+      <c r="C5" s="478" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="479"/>
+      <c r="E5" s="479"/>
+      <c r="F5" s="479"/>
+      <c r="G5" s="480"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1">
       <c r="B6" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="467" t="s">
+      <c r="C6" s="478" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="468"/>
-      <c r="E6" s="468"/>
-      <c r="F6" s="468"/>
-      <c r="G6" s="469"/>
+      <c r="D6" s="479"/>
+      <c r="E6" s="479"/>
+      <c r="F6" s="479"/>
+      <c r="G6" s="480"/>
       <c r="I6" s="101" t="s">
         <v>58</v>
       </c>
@@ -54682,13 +54600,13 @@
       <c r="B8" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="467">
+      <c r="C8" s="478">
         <v>1</v>
       </c>
-      <c r="D8" s="468"/>
-      <c r="E8" s="468"/>
-      <c r="F8" s="468"/>
-      <c r="G8" s="469"/>
+      <c r="D8" s="479"/>
+      <c r="E8" s="479"/>
+      <c r="F8" s="479"/>
+      <c r="G8" s="480"/>
       <c r="I8" s="107">
         <v>50</v>
       </c>
@@ -54702,13 +54620,13 @@
       <c r="B9" s="99" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="467" t="s">
-        <v>157</v>
-      </c>
-      <c r="D9" s="468"/>
-      <c r="E9" s="468"/>
-      <c r="F9" s="468"/>
-      <c r="G9" s="469"/>
+      <c r="C9" s="478" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="479"/>
+      <c r="E9" s="479"/>
+      <c r="F9" s="479"/>
+      <c r="G9" s="480"/>
       <c r="I9" s="107">
         <v>4</v>
       </c>
@@ -54722,13 +54640,13 @@
       <c r="B10" s="99" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="467" t="s">
-        <v>157</v>
-      </c>
-      <c r="D10" s="468"/>
-      <c r="E10" s="468"/>
-      <c r="F10" s="468"/>
-      <c r="G10" s="469"/>
+      <c r="C10" s="478" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="479"/>
+      <c r="E10" s="479"/>
+      <c r="F10" s="479"/>
+      <c r="G10" s="480"/>
       <c r="I10" s="107">
         <f>E16</f>
         <v>1</v>
@@ -54752,13 +54670,13 @@
       <c r="B11" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="467" t="s">
-        <v>139</v>
-      </c>
-      <c r="D11" s="468"/>
-      <c r="E11" s="468"/>
-      <c r="F11" s="468"/>
-      <c r="G11" s="469"/>
+      <c r="C11" s="478" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="479"/>
+      <c r="E11" s="479"/>
+      <c r="F11" s="479"/>
+      <c r="G11" s="480"/>
       <c r="I11" s="107">
         <f>F16</f>
         <v>0</v>
@@ -54773,22 +54691,22 @@
       <c r="P11" s="109"/>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1">
-      <c r="B12" s="479" t="s">
+      <c r="B12" s="481" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="480"/>
-      <c r="D12" s="480"/>
-      <c r="E12" s="480"/>
-      <c r="F12" s="480"/>
-      <c r="G12" s="481"/>
+      <c r="C12" s="482"/>
+      <c r="D12" s="482"/>
+      <c r="E12" s="482"/>
+      <c r="F12" s="482"/>
+      <c r="G12" s="483"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1">
-      <c r="B13" s="476"/>
-      <c r="C13" s="477"/>
-      <c r="D13" s="477"/>
-      <c r="E13" s="477"/>
-      <c r="F13" s="477"/>
-      <c r="G13" s="478"/>
+      <c r="B13" s="475"/>
+      <c r="C13" s="476"/>
+      <c r="D13" s="476"/>
+      <c r="E13" s="476"/>
+      <c r="F13" s="476"/>
+      <c r="G13" s="477"/>
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1">
       <c r="B14" s="113" t="s">
@@ -54922,21 +54840,21 @@
       <c r="R18" s="116"/>
     </row>
     <row r="19" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B19" s="482" t="s">
+      <c r="B19" s="484" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="465"/>
-      <c r="D19" s="465"/>
-      <c r="E19" s="465"/>
-      <c r="F19" s="465"/>
-      <c r="G19" s="466"/>
+      <c r="C19" s="485"/>
+      <c r="D19" s="485"/>
+      <c r="E19" s="485"/>
+      <c r="F19" s="485"/>
+      <c r="G19" s="486"/>
     </row>
     <row r="20" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B20" s="483" t="s">
+      <c r="B20" s="487" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="465"/>
-      <c r="D20" s="466"/>
+      <c r="C20" s="485"/>
+      <c r="D20" s="486"/>
       <c r="E20" s="131"/>
       <c r="F20" s="131" t="s">
         <v>78</v>
@@ -54946,11 +54864,11 @@
       </c>
     </row>
     <row r="21" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B21" s="484" t="s">
+      <c r="B21" s="488" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="465"/>
-      <c r="D21" s="466"/>
+      <c r="C21" s="485"/>
+      <c r="D21" s="486"/>
       <c r="E21" s="132"/>
       <c r="F21" s="132" t="s">
         <v>81</v>
@@ -54960,11 +54878,11 @@
       </c>
     </row>
     <row r="22" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B22" s="484" t="s">
+      <c r="B22" s="488" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="465"/>
-      <c r="D22" s="466"/>
+      <c r="C22" s="485"/>
+      <c r="D22" s="486"/>
       <c r="E22" s="132"/>
       <c r="F22" s="132" t="s">
         <v>81</v>
@@ -54975,306 +54893,306 @@
     </row>
     <row r="23" spans="2:18" ht="15.75" customHeight="1"/>
     <row r="24" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B24" s="489"/>
-      <c r="C24" s="485" t="s">
+      <c r="B24" s="491"/>
+      <c r="C24" s="489" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="488" t="s">
+      <c r="D24" s="490" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="471"/>
-      <c r="F24" s="471"/>
-      <c r="G24" s="472"/>
+      <c r="E24" s="470"/>
+      <c r="F24" s="470"/>
+      <c r="G24" s="471"/>
     </row>
     <row r="25" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B25" s="486"/>
-      <c r="C25" s="486"/>
-      <c r="D25" s="473"/>
-      <c r="E25" s="474"/>
-      <c r="F25" s="474"/>
-      <c r="G25" s="475"/>
+      <c r="B25" s="465"/>
+      <c r="C25" s="465"/>
+      <c r="D25" s="472"/>
+      <c r="E25" s="473"/>
+      <c r="F25" s="473"/>
+      <c r="G25" s="474"/>
     </row>
     <row r="26" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B26" s="486"/>
-      <c r="C26" s="486"/>
-      <c r="D26" s="473"/>
-      <c r="E26" s="474"/>
-      <c r="F26" s="474"/>
-      <c r="G26" s="475"/>
+      <c r="B26" s="465"/>
+      <c r="C26" s="465"/>
+      <c r="D26" s="472"/>
+      <c r="E26" s="473"/>
+      <c r="F26" s="473"/>
+      <c r="G26" s="474"/>
     </row>
     <row r="27" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B27" s="487"/>
-      <c r="C27" s="487"/>
-      <c r="D27" s="476"/>
-      <c r="E27" s="477"/>
-      <c r="F27" s="477"/>
-      <c r="G27" s="478"/>
+      <c r="B27" s="466"/>
+      <c r="C27" s="466"/>
+      <c r="D27" s="475"/>
+      <c r="E27" s="476"/>
+      <c r="F27" s="476"/>
+      <c r="G27" s="477"/>
     </row>
     <row r="28" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B28" s="490" t="s">
+      <c r="B28" s="467" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="491" t="s">
+      <c r="C28" s="464" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="470" t="s">
+      <c r="D28" s="469" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="471"/>
-      <c r="F28" s="471"/>
-      <c r="G28" s="472"/>
+      <c r="E28" s="470"/>
+      <c r="F28" s="470"/>
+      <c r="G28" s="471"/>
     </row>
     <row r="29" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B29" s="486"/>
-      <c r="C29" s="486"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
-      <c r="G29" s="475"/>
+      <c r="B29" s="465"/>
+      <c r="C29" s="465"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
+      <c r="G29" s="474"/>
     </row>
     <row r="30" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B30" s="486"/>
-      <c r="C30" s="486"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="474"/>
-      <c r="F30" s="474"/>
-      <c r="G30" s="475"/>
+      <c r="B30" s="465"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
+      <c r="G30" s="474"/>
     </row>
     <row r="31" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B31" s="487"/>
-      <c r="C31" s="487"/>
-      <c r="D31" s="476"/>
-      <c r="E31" s="477"/>
-      <c r="F31" s="477"/>
-      <c r="G31" s="478"/>
+      <c r="B31" s="466"/>
+      <c r="C31" s="466"/>
+      <c r="D31" s="475"/>
+      <c r="E31" s="476"/>
+      <c r="F31" s="476"/>
+      <c r="G31" s="477"/>
     </row>
     <row r="32" spans="2:18" ht="15.75" customHeight="1">
-      <c r="B32" s="490" t="s">
+      <c r="B32" s="467" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="491" t="s">
+      <c r="C32" s="464" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="470" t="s">
+      <c r="D32" s="469" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="471"/>
-      <c r="F32" s="471"/>
-      <c r="G32" s="472"/>
+      <c r="E32" s="470"/>
+      <c r="F32" s="470"/>
+      <c r="G32" s="471"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B33" s="486"/>
-      <c r="C33" s="486"/>
-      <c r="D33" s="473"/>
-      <c r="E33" s="474"/>
-      <c r="F33" s="474"/>
-      <c r="G33" s="475"/>
+      <c r="B33" s="465"/>
+      <c r="C33" s="465"/>
+      <c r="D33" s="472"/>
+      <c r="E33" s="473"/>
+      <c r="F33" s="473"/>
+      <c r="G33" s="474"/>
     </row>
     <row r="34" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B34" s="486"/>
-      <c r="C34" s="486"/>
-      <c r="D34" s="473"/>
-      <c r="E34" s="474"/>
-      <c r="F34" s="474"/>
-      <c r="G34" s="475"/>
+      <c r="B34" s="465"/>
+      <c r="C34" s="465"/>
+      <c r="D34" s="472"/>
+      <c r="E34" s="473"/>
+      <c r="F34" s="473"/>
+      <c r="G34" s="474"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B35" s="487"/>
-      <c r="C35" s="487"/>
-      <c r="D35" s="476"/>
-      <c r="E35" s="477"/>
-      <c r="F35" s="477"/>
-      <c r="G35" s="478"/>
+      <c r="B35" s="466"/>
+      <c r="C35" s="466"/>
+      <c r="D35" s="475"/>
+      <c r="E35" s="476"/>
+      <c r="F35" s="476"/>
+      <c r="G35" s="477"/>
     </row>
     <row r="36" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B36" s="490" t="s">
+      <c r="B36" s="467" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="491" t="s">
+      <c r="C36" s="464" t="s">
         <v>90</v>
       </c>
-      <c r="D36" s="470" t="s">
+      <c r="D36" s="469" t="s">
         <v>91</v>
       </c>
-      <c r="E36" s="471"/>
-      <c r="F36" s="471"/>
-      <c r="G36" s="472"/>
+      <c r="E36" s="470"/>
+      <c r="F36" s="470"/>
+      <c r="G36" s="471"/>
     </row>
     <row r="37" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B37" s="486"/>
-      <c r="C37" s="486"/>
-      <c r="D37" s="473"/>
-      <c r="E37" s="474"/>
-      <c r="F37" s="474"/>
-      <c r="G37" s="475"/>
+      <c r="B37" s="465"/>
+      <c r="C37" s="465"/>
+      <c r="D37" s="472"/>
+      <c r="E37" s="473"/>
+      <c r="F37" s="473"/>
+      <c r="G37" s="474"/>
     </row>
     <row r="38" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B38" s="486"/>
-      <c r="C38" s="486"/>
-      <c r="D38" s="473"/>
-      <c r="E38" s="474"/>
-      <c r="F38" s="474"/>
-      <c r="G38" s="475"/>
+      <c r="B38" s="465"/>
+      <c r="C38" s="465"/>
+      <c r="D38" s="472"/>
+      <c r="E38" s="473"/>
+      <c r="F38" s="473"/>
+      <c r="G38" s="474"/>
     </row>
     <row r="39" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B39" s="487"/>
-      <c r="C39" s="487"/>
-      <c r="D39" s="476"/>
-      <c r="E39" s="477"/>
-      <c r="F39" s="477"/>
-      <c r="G39" s="478"/>
+      <c r="B39" s="466"/>
+      <c r="C39" s="466"/>
+      <c r="D39" s="475"/>
+      <c r="E39" s="476"/>
+      <c r="F39" s="476"/>
+      <c r="G39" s="477"/>
     </row>
     <row r="40" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B40" s="490" t="s">
+      <c r="B40" s="467" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="491" t="s">
+      <c r="C40" s="464" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="470" t="s">
+      <c r="D40" s="469" t="s">
         <v>93</v>
       </c>
-      <c r="E40" s="471"/>
-      <c r="F40" s="471"/>
-      <c r="G40" s="472"/>
+      <c r="E40" s="470"/>
+      <c r="F40" s="470"/>
+      <c r="G40" s="471"/>
     </row>
     <row r="41" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B41" s="486"/>
-      <c r="C41" s="486"/>
-      <c r="D41" s="473"/>
-      <c r="E41" s="474"/>
-      <c r="F41" s="474"/>
-      <c r="G41" s="475"/>
+      <c r="B41" s="465"/>
+      <c r="C41" s="465"/>
+      <c r="D41" s="472"/>
+      <c r="E41" s="473"/>
+      <c r="F41" s="473"/>
+      <c r="G41" s="474"/>
     </row>
     <row r="42" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B42" s="486"/>
-      <c r="C42" s="486"/>
-      <c r="D42" s="473"/>
-      <c r="E42" s="474"/>
-      <c r="F42" s="474"/>
-      <c r="G42" s="475"/>
+      <c r="B42" s="465"/>
+      <c r="C42" s="465"/>
+      <c r="D42" s="472"/>
+      <c r="E42" s="473"/>
+      <c r="F42" s="473"/>
+      <c r="G42" s="474"/>
     </row>
     <row r="43" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B43" s="487"/>
-      <c r="C43" s="487"/>
-      <c r="D43" s="476"/>
-      <c r="E43" s="477"/>
-      <c r="F43" s="477"/>
-      <c r="G43" s="478"/>
+      <c r="B43" s="466"/>
+      <c r="C43" s="466"/>
+      <c r="D43" s="475"/>
+      <c r="E43" s="476"/>
+      <c r="F43" s="476"/>
+      <c r="G43" s="477"/>
     </row>
     <row r="44" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B44" s="490" t="s">
+      <c r="B44" s="467" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="492" t="s">
+      <c r="C44" s="468" t="s">
         <v>94</v>
       </c>
-      <c r="D44" s="470" t="s">
+      <c r="D44" s="469" t="s">
         <v>95</v>
       </c>
-      <c r="E44" s="471"/>
-      <c r="F44" s="471"/>
-      <c r="G44" s="472"/>
+      <c r="E44" s="470"/>
+      <c r="F44" s="470"/>
+      <c r="G44" s="471"/>
     </row>
     <row r="45" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B45" s="486"/>
-      <c r="C45" s="486"/>
-      <c r="D45" s="473"/>
-      <c r="E45" s="474"/>
-      <c r="F45" s="474"/>
-      <c r="G45" s="475"/>
+      <c r="B45" s="465"/>
+      <c r="C45" s="465"/>
+      <c r="D45" s="472"/>
+      <c r="E45" s="473"/>
+      <c r="F45" s="473"/>
+      <c r="G45" s="474"/>
     </row>
     <row r="46" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B46" s="486"/>
-      <c r="C46" s="486"/>
-      <c r="D46" s="473"/>
-      <c r="E46" s="474"/>
-      <c r="F46" s="474"/>
-      <c r="G46" s="475"/>
+      <c r="B46" s="465"/>
+      <c r="C46" s="465"/>
+      <c r="D46" s="472"/>
+      <c r="E46" s="473"/>
+      <c r="F46" s="473"/>
+      <c r="G46" s="474"/>
     </row>
     <row r="47" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B47" s="487"/>
-      <c r="C47" s="487"/>
-      <c r="D47" s="476"/>
-      <c r="E47" s="477"/>
-      <c r="F47" s="477"/>
-      <c r="G47" s="478"/>
+      <c r="B47" s="466"/>
+      <c r="C47" s="466"/>
+      <c r="D47" s="475"/>
+      <c r="E47" s="476"/>
+      <c r="F47" s="476"/>
+      <c r="G47" s="477"/>
     </row>
     <row r="48" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B48" s="490" t="s">
+      <c r="B48" s="467" t="s">
         <v>85</v>
       </c>
-      <c r="C48" s="492" t="s">
+      <c r="C48" s="468" t="s">
         <v>96</v>
       </c>
-      <c r="D48" s="470" t="s">
+      <c r="D48" s="469" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="471"/>
-      <c r="F48" s="471"/>
-      <c r="G48" s="472"/>
+      <c r="E48" s="470"/>
+      <c r="F48" s="470"/>
+      <c r="G48" s="471"/>
     </row>
     <row r="49" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B49" s="486"/>
-      <c r="C49" s="486"/>
-      <c r="D49" s="473"/>
-      <c r="E49" s="474"/>
-      <c r="F49" s="474"/>
-      <c r="G49" s="475"/>
+      <c r="B49" s="465"/>
+      <c r="C49" s="465"/>
+      <c r="D49" s="472"/>
+      <c r="E49" s="473"/>
+      <c r="F49" s="473"/>
+      <c r="G49" s="474"/>
     </row>
     <row r="50" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B50" s="486"/>
-      <c r="C50" s="486"/>
-      <c r="D50" s="473"/>
-      <c r="E50" s="474"/>
-      <c r="F50" s="474"/>
-      <c r="G50" s="475"/>
+      <c r="B50" s="465"/>
+      <c r="C50" s="465"/>
+      <c r="D50" s="472"/>
+      <c r="E50" s="473"/>
+      <c r="F50" s="473"/>
+      <c r="G50" s="474"/>
     </row>
     <row r="51" spans="2:7" ht="33.75" customHeight="1">
-      <c r="B51" s="487"/>
-      <c r="C51" s="487"/>
-      <c r="D51" s="476"/>
-      <c r="E51" s="477"/>
-      <c r="F51" s="477"/>
-      <c r="G51" s="478"/>
+      <c r="B51" s="466"/>
+      <c r="C51" s="466"/>
+      <c r="D51" s="475"/>
+      <c r="E51" s="476"/>
+      <c r="F51" s="476"/>
+      <c r="G51" s="477"/>
     </row>
     <row r="52" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B52" s="490" t="s">
+      <c r="B52" s="467" t="s">
         <v>85</v>
       </c>
-      <c r="C52" s="492" t="s">
+      <c r="C52" s="468" t="s">
         <v>98</v>
       </c>
-      <c r="D52" s="470" t="s">
+      <c r="D52" s="469" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="471"/>
-      <c r="F52" s="471"/>
-      <c r="G52" s="472"/>
+      <c r="E52" s="470"/>
+      <c r="F52" s="470"/>
+      <c r="G52" s="471"/>
     </row>
     <row r="53" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B53" s="486"/>
-      <c r="C53" s="486"/>
-      <c r="D53" s="473"/>
-      <c r="E53" s="474"/>
-      <c r="F53" s="474"/>
-      <c r="G53" s="475"/>
+      <c r="B53" s="465"/>
+      <c r="C53" s="465"/>
+      <c r="D53" s="472"/>
+      <c r="E53" s="473"/>
+      <c r="F53" s="473"/>
+      <c r="G53" s="474"/>
     </row>
     <row r="54" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B54" s="486"/>
-      <c r="C54" s="486"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
-      <c r="G54" s="475"/>
+      <c r="B54" s="465"/>
+      <c r="C54" s="465"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
+      <c r="G54" s="474"/>
     </row>
     <row r="55" spans="2:7" ht="39" customHeight="1">
-      <c r="B55" s="487"/>
-      <c r="C55" s="487"/>
-      <c r="D55" s="476"/>
-      <c r="E55" s="477"/>
-      <c r="F55" s="477"/>
-      <c r="G55" s="478"/>
+      <c r="B55" s="466"/>
+      <c r="C55" s="466"/>
+      <c r="D55" s="475"/>
+      <c r="E55" s="476"/>
+      <c r="F55" s="476"/>
+      <c r="G55" s="477"/>
     </row>
     <row r="56" spans="2:7" ht="15.75" customHeight="1"/>
     <row r="57" spans="2:7" ht="15.75" customHeight="1"/>
@@ -56223,21 +56141,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="C36:C39"/>
-    <mergeCell ref="B48:B51"/>
-    <mergeCell ref="C48:C51"/>
-    <mergeCell ref="D48:G51"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="C52:C55"/>
-    <mergeCell ref="D52:G55"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="C40:C43"/>
-    <mergeCell ref="D40:G43"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="D44:G47"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="D28:G31"/>
@@ -56254,11 +56162,21 @@
     <mergeCell ref="B28:B31"/>
     <mergeCell ref="C28:C31"/>
     <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="D48:G51"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="C52:C55"/>
+    <mergeCell ref="D52:G55"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="D40:G43"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="C44:C47"/>
+    <mergeCell ref="D44:G47"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="C36:C39"/>
+    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="C48:C51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -56281,52 +56199,52 @@
     <row r="1" spans="2:3" ht="12.75" customHeight="1"/>
     <row r="2" spans="2:3" ht="12.75" customHeight="1"/>
     <row r="3" spans="2:3" ht="9" customHeight="1">
-      <c r="B3" s="493" t="s">
+      <c r="B3" s="499" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="472"/>
+      <c r="C3" s="471"/>
     </row>
     <row r="4" spans="2:3" ht="13.5" customHeight="1">
-      <c r="B4" s="473"/>
-      <c r="C4" s="475"/>
+      <c r="B4" s="472"/>
+      <c r="C4" s="474"/>
     </row>
     <row r="5" spans="2:3" ht="13.5" customHeight="1">
-      <c r="B5" s="473"/>
-      <c r="C5" s="475"/>
+      <c r="B5" s="472"/>
+      <c r="C5" s="474"/>
     </row>
     <row r="6" spans="2:3" ht="2.25" customHeight="1">
-      <c r="B6" s="476"/>
-      <c r="C6" s="478"/>
+      <c r="B6" s="475"/>
+      <c r="C6" s="477"/>
     </row>
     <row r="7" spans="2:3" ht="7.5" customHeight="1">
-      <c r="B7" s="494" t="s">
-        <v>322</v>
-      </c>
-      <c r="C7" s="472"/>
+      <c r="B7" s="497" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="471"/>
     </row>
     <row r="8" spans="2:3" ht="6.75" customHeight="1">
-      <c r="B8" s="473"/>
-      <c r="C8" s="475"/>
+      <c r="B8" s="472"/>
+      <c r="C8" s="474"/>
     </row>
     <row r="9" spans="2:3" ht="13.5" customHeight="1">
-      <c r="B9" s="495" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" s="496"/>
+      <c r="B9" s="493" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="500"/>
     </row>
     <row r="10" spans="2:3" ht="12" customHeight="1">
-      <c r="B10" s="497"/>
-      <c r="C10" s="498"/>
+      <c r="B10" s="501"/>
+      <c r="C10" s="502"/>
     </row>
     <row r="11" spans="2:3" ht="15" customHeight="1">
-      <c r="B11" s="499" t="s">
+      <c r="B11" s="494" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="500"/>
+      <c r="C11" s="495"/>
     </row>
     <row r="12" spans="2:3" ht="13.5" customHeight="1">
       <c r="B12" s="133" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C12" s="134"/>
     </row>
@@ -56338,40 +56256,40 @@
     </row>
     <row r="14" spans="2:3" ht="21" customHeight="1">
       <c r="B14" s="135" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C14" s="134"/>
     </row>
     <row r="15" spans="2:3" ht="20.25" customHeight="1">
       <c r="B15" s="135" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C15" s="134"/>
     </row>
     <row r="16" spans="2:3" ht="18.75" customHeight="1">
       <c r="B16" s="135" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C16" s="134"/>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1">
       <c r="A17" s="136"/>
       <c r="B17" s="294" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C17" s="134"/>
     </row>
     <row r="18" spans="1:3" ht="16.5" customHeight="1">
       <c r="A18" s="136"/>
       <c r="B18" s="137" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C18" s="138"/>
     </row>
     <row r="19" spans="1:3" ht="19.5" customHeight="1">
       <c r="A19" s="136"/>
       <c r="B19" s="139" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C19" s="140"/>
     </row>
@@ -56383,82 +56301,82 @@
       <c r="C21" s="142"/>
     </row>
     <row r="22" spans="1:3" ht="13.5" customHeight="1">
-      <c r="B22" s="501" t="s">
+      <c r="B22" s="496" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="472"/>
+      <c r="C22" s="471"/>
     </row>
     <row r="23" spans="1:3" ht="10.5" customHeight="1">
-      <c r="B23" s="473"/>
-      <c r="C23" s="475"/>
+      <c r="B23" s="472"/>
+      <c r="C23" s="474"/>
     </row>
     <row r="24" spans="1:3" ht="13.5" hidden="1" customHeight="1">
-      <c r="B24" s="473"/>
-      <c r="C24" s="475"/>
+      <c r="B24" s="472"/>
+      <c r="C24" s="474"/>
     </row>
     <row r="25" spans="1:3" ht="13.5" hidden="1" customHeight="1">
-      <c r="B25" s="476"/>
-      <c r="C25" s="478"/>
+      <c r="B25" s="475"/>
+      <c r="C25" s="477"/>
     </row>
     <row r="26" spans="1:3" ht="12.75" customHeight="1">
-      <c r="B26" s="494" t="s">
-        <v>321</v>
-      </c>
-      <c r="C26" s="472"/>
+      <c r="B26" s="497" t="s">
+        <v>313</v>
+      </c>
+      <c r="C26" s="471"/>
     </row>
     <row r="27" spans="1:3" ht="12.75" customHeight="1">
-      <c r="B27" s="473"/>
-      <c r="C27" s="475"/>
+      <c r="B27" s="472"/>
+      <c r="C27" s="474"/>
     </row>
     <row r="28" spans="1:3" ht="12.75" customHeight="1">
-      <c r="B28" s="495" t="s">
-        <v>193</v>
-      </c>
-      <c r="C28" s="481"/>
+      <c r="B28" s="493" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="483"/>
     </row>
     <row r="29" spans="1:3" ht="12.75" customHeight="1">
-      <c r="B29" s="473"/>
-      <c r="C29" s="475"/>
+      <c r="B29" s="472"/>
+      <c r="C29" s="474"/>
     </row>
     <row r="30" spans="1:3" ht="12.75" customHeight="1">
-      <c r="B30" s="499" t="s">
+      <c r="B30" s="494" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="500"/>
+      <c r="C30" s="495"/>
     </row>
     <row r="31" spans="1:3" ht="17.25" customHeight="1">
       <c r="B31" s="133" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C31" s="134"/>
     </row>
     <row r="32" spans="1:3" ht="12.75" customHeight="1">
       <c r="B32" s="135" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C32" s="134"/>
     </row>
     <row r="33" spans="2:5" ht="12.75" customHeight="1">
       <c r="B33" s="135" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C33" s="134"/>
     </row>
     <row r="34" spans="2:5" ht="12.75" customHeight="1">
       <c r="B34" s="135" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C34" s="134"/>
     </row>
     <row r="35" spans="2:5" ht="12.75" customHeight="1">
       <c r="B35" s="294" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C35" s="134"/>
     </row>
     <row r="36" spans="2:5" ht="12.75" customHeight="1">
       <c r="B36" s="143" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C36" s="140"/>
     </row>
@@ -56476,88 +56394,88 @@
       <c r="D40" s="145"/>
     </row>
     <row r="41" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B41" s="501" t="s">
+      <c r="B41" s="496" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="472"/>
+      <c r="C41" s="471"/>
       <c r="E41" s="146"/>
     </row>
     <row r="42" spans="2:5" ht="13.5" customHeight="1">
-      <c r="B42" s="473"/>
-      <c r="C42" s="475"/>
+      <c r="B42" s="472"/>
+      <c r="C42" s="474"/>
       <c r="E42" s="146"/>
     </row>
     <row r="43" spans="2:5" ht="6.75" customHeight="1">
-      <c r="B43" s="473"/>
-      <c r="C43" s="475"/>
+      <c r="B43" s="472"/>
+      <c r="C43" s="474"/>
       <c r="E43" s="146"/>
     </row>
     <row r="44" spans="2:5" ht="12.75" hidden="1" customHeight="1">
-      <c r="B44" s="476"/>
-      <c r="C44" s="478"/>
+      <c r="B44" s="475"/>
+      <c r="C44" s="477"/>
       <c r="E44" s="146"/>
     </row>
     <row r="45" spans="2:5" ht="12.75" customHeight="1">
-      <c r="B45" s="494" t="s">
-        <v>320</v>
-      </c>
-      <c r="C45" s="472"/>
+      <c r="B45" s="497" t="s">
+        <v>312</v>
+      </c>
+      <c r="C45" s="471"/>
       <c r="E45" s="146"/>
     </row>
     <row r="46" spans="2:5" ht="12.75" customHeight="1">
-      <c r="B46" s="473"/>
-      <c r="C46" s="475"/>
+      <c r="B46" s="472"/>
+      <c r="C46" s="474"/>
       <c r="E46" s="146"/>
     </row>
     <row r="47" spans="2:5" ht="12.75" customHeight="1">
       <c r="B47" s="147" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C47" s="148"/>
       <c r="E47" s="146"/>
     </row>
     <row r="48" spans="2:5" ht="12.75" customHeight="1">
-      <c r="B48" s="502" t="s">
+      <c r="B48" s="498" t="s">
         <v>101</v>
       </c>
-      <c r="C48" s="500"/>
+      <c r="C48" s="495"/>
       <c r="E48" s="146"/>
     </row>
     <row r="49" spans="1:26" ht="12.75" customHeight="1">
       <c r="B49" s="149" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C49" s="150"/>
       <c r="E49" s="142"/>
     </row>
     <row r="50" spans="1:26" ht="12.75" customHeight="1">
       <c r="B50" s="149" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C50" s="150"/>
       <c r="E50" s="142"/>
     </row>
     <row r="51" spans="1:26" ht="12.75" customHeight="1">
       <c r="B51" s="151" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C51" s="150"/>
     </row>
     <row r="52" spans="1:26" ht="12.75" customHeight="1">
       <c r="B52" s="135" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C52" s="150"/>
     </row>
     <row r="53" spans="1:26" ht="12.75" customHeight="1">
       <c r="B53" s="135" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C53" s="150"/>
     </row>
     <row r="54" spans="1:26" ht="12.75" customHeight="1">
       <c r="B54" s="302" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C54" s="150"/>
     </row>
@@ -56591,7 +56509,7 @@
     <row r="56" spans="1:26" ht="12.75" customHeight="1">
       <c r="A56" s="142"/>
       <c r="B56" s="143" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C56" s="153"/>
       <c r="D56" s="142"/>
@@ -56625,79 +56543,79 @@
       <c r="C58" s="142"/>
     </row>
     <row r="59" spans="1:26" ht="13.5" customHeight="1">
-      <c r="B59" s="501" t="s">
+      <c r="B59" s="496" t="s">
         <v>100</v>
       </c>
-      <c r="C59" s="472"/>
+      <c r="C59" s="471"/>
     </row>
     <row r="60" spans="1:26" ht="13.5" customHeight="1">
-      <c r="B60" s="473"/>
-      <c r="C60" s="475"/>
+      <c r="B60" s="472"/>
+      <c r="C60" s="474"/>
     </row>
     <row r="61" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B61" s="473"/>
-      <c r="C61" s="475"/>
+      <c r="B61" s="472"/>
+      <c r="C61" s="474"/>
     </row>
     <row r="62" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B62" s="476"/>
-      <c r="C62" s="478"/>
+      <c r="B62" s="475"/>
+      <c r="C62" s="477"/>
     </row>
     <row r="63" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B63" s="494" t="s">
-        <v>106</v>
-      </c>
-      <c r="C63" s="472"/>
+      <c r="B63" s="497" t="s">
+        <v>104</v>
+      </c>
+      <c r="C63" s="471"/>
     </row>
     <row r="64" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B64" s="473"/>
-      <c r="C64" s="475"/>
+      <c r="B64" s="472"/>
+      <c r="C64" s="474"/>
     </row>
     <row r="65" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B65" s="495" t="s">
-        <v>249</v>
-      </c>
-      <c r="C65" s="481"/>
+      <c r="B65" s="493" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="483"/>
     </row>
     <row r="66" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B66" s="473"/>
-      <c r="C66" s="475"/>
+      <c r="B66" s="472"/>
+      <c r="C66" s="474"/>
     </row>
     <row r="67" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B67" s="499" t="s">
+      <c r="B67" s="494" t="s">
         <v>101</v>
       </c>
-      <c r="C67" s="500"/>
+      <c r="C67" s="495"/>
     </row>
     <row r="68" spans="1:26" ht="12.75" customHeight="1">
       <c r="B68" s="133" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C68" s="134"/>
       <c r="E68" s="142"/>
     </row>
     <row r="69" spans="1:26" ht="12.75" customHeight="1">
       <c r="B69" s="135" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C69" s="134"/>
       <c r="E69" s="142"/>
     </row>
     <row r="70" spans="1:26" ht="12.75" customHeight="1">
       <c r="B70" s="135" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C70" s="134"/>
     </row>
     <row r="71" spans="1:26" ht="12.75" customHeight="1">
       <c r="B71" s="135" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C71" s="134"/>
     </row>
     <row r="72" spans="1:26" ht="12.75" customHeight="1">
       <c r="A72" s="142"/>
       <c r="B72" s="302" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C72" s="134"/>
       <c r="F72" s="142"/>
@@ -56724,7 +56642,7 @@
     </row>
     <row r="73" spans="1:26" ht="12.75" customHeight="1">
       <c r="B73" s="143" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C73" s="140"/>
     </row>
@@ -56735,69 +56653,22 @@
     <row r="76" spans="1:26" ht="13.5" customHeight="1"/>
     <row r="77" spans="1:26" ht="13.5" customHeight="1"/>
     <row r="78" spans="1:26" ht="12.75" customHeight="1"/>
-    <row r="79" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B79" s="494" t="s">
-        <v>108</v>
-      </c>
-      <c r="C79" s="472"/>
-    </row>
-    <row r="80" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B80" s="473"/>
-      <c r="C80" s="475"/>
-    </row>
-    <row r="81" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B81" s="495" t="s">
-        <v>109</v>
-      </c>
-      <c r="C81" s="481"/>
-    </row>
-    <row r="82" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B82" s="473"/>
-      <c r="C82" s="475"/>
-    </row>
-    <row r="83" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B83" s="499" t="s">
-        <v>101</v>
-      </c>
-      <c r="C83" s="500"/>
-    </row>
-    <row r="84" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B84" s="133" t="s">
-        <v>103</v>
-      </c>
-      <c r="C84" s="134"/>
-    </row>
-    <row r="85" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B85" s="135" t="s">
-        <v>110</v>
-      </c>
-      <c r="C85" s="134"/>
-    </row>
-    <row r="86" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B86" s="135" t="s">
-        <v>104</v>
-      </c>
-      <c r="C86" s="134"/>
-    </row>
-    <row r="87" spans="1:26" ht="12.75" customHeight="1">
-      <c r="B87" s="135" t="s">
-        <v>111</v>
-      </c>
-      <c r="C87" s="134"/>
-    </row>
+    <row r="79" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="80" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="81" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="82" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="83" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="84" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="85" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="86" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="87" spans="1:26" ht="12.75" customHeight="1"/>
     <row r="88" spans="1:26" ht="12.75" customHeight="1">
       <c r="A88" s="154"/>
-      <c r="B88" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C88" s="134"/>
     </row>
     <row r="89" spans="1:26" ht="12.75" customHeight="1">
       <c r="A89" s="136"/>
-      <c r="B89" s="139" t="s">
-        <v>113</v>
-      </c>
-      <c r="C89" s="140"/>
+      <c r="D89" s="142"/>
+      <c r="E89" s="142"/>
       <c r="F89" s="142"/>
       <c r="G89" s="142"/>
       <c r="H89" s="142"/>
@@ -56817,8 +56688,6 @@
       <c r="V89" s="142"/>
       <c r="W89" s="142"/>
       <c r="X89" s="142"/>
-      <c r="Y89" s="142"/>
-      <c r="Z89" s="142"/>
     </row>
     <row r="90" spans="1:26" ht="12.75" customHeight="1">
       <c r="A90" s="142"/>
@@ -57759,9 +57628,15 @@
     <row r="1001" ht="12.75" customHeight="1"/>
     <row r="1002" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B81:C82"/>
-    <mergeCell ref="B83:C83"/>
+  <mergeCells count="15">
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B3:C6"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B9:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B22:C25"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B41:C44"/>
     <mergeCell ref="B45:C46"/>
@@ -57769,22 +57644,12 @@
     <mergeCell ref="B59:C62"/>
     <mergeCell ref="B63:C64"/>
     <mergeCell ref="B65:C66"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B79:C80"/>
-    <mergeCell ref="B3:C6"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B9:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B22:C25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B17" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
     <hyperlink ref="B35" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
     <hyperlink ref="B54" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
     <hyperlink ref="B72" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
-    <hyperlink ref="B88" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -57812,20 +57677,20 @@
     </row>
     <row r="3" spans="1:26" ht="13.5" customHeight="1">
       <c r="B3" s="503" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="471"/>
-      <c r="D3" s="471"/>
-      <c r="E3" s="472"/>
+        <v>106</v>
+      </c>
+      <c r="C3" s="470"/>
+      <c r="D3" s="470"/>
+      <c r="E3" s="471"/>
       <c r="F3" s="157"/>
       <c r="G3" s="157"/>
       <c r="H3" s="157"/>
     </row>
     <row r="4" spans="1:26" ht="45.75" customHeight="1">
-      <c r="B4" s="476"/>
-      <c r="C4" s="477"/>
-      <c r="D4" s="477"/>
-      <c r="E4" s="478"/>
+      <c r="B4" s="475"/>
+      <c r="C4" s="476"/>
+      <c r="D4" s="476"/>
+      <c r="E4" s="477"/>
       <c r="F4" s="157"/>
       <c r="G4" s="157"/>
       <c r="H4" s="157"/>
@@ -57835,13 +57700,13 @@
         <v>37</v>
       </c>
       <c r="C5" s="159" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D5" s="159" t="s">
         <v>84</v>
       </c>
       <c r="E5" s="159" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="27.75" customHeight="1">
@@ -57850,13 +57715,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="161" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D6" s="162" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E6" s="160" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -57886,13 +57751,13 @@
         <v>2</v>
       </c>
       <c r="C7" s="163" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D7" s="164" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E7" s="160" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -57922,13 +57787,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="163" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D8" s="164" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E8" s="160" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="F8" s="165"/>
       <c r="G8" s="165"/>
@@ -57958,13 +57823,13 @@
         <v>4</v>
       </c>
       <c r="C9" s="163" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D9" s="164" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E9" s="160" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="F9" s="165"/>
       <c r="G9" s="165"/>
@@ -57994,13 +57859,13 @@
         <v>5</v>
       </c>
       <c r="C10" s="163" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D10" s="164" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E10" s="160" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F10" s="165"/>
       <c r="G10" s="165"/>
@@ -58030,10 +57895,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="163" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D11" s="164" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="E11" s="160">
         <v>2.5</v>
@@ -58066,10 +57931,10 @@
         <v>7</v>
       </c>
       <c r="C12" s="163" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D12" s="164" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E12" s="160" t="s">
         <v>50</v>
@@ -58102,10 +57967,10 @@
         <v>8</v>
       </c>
       <c r="C13" s="163" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D13" s="164" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E13" s="160" t="s">
         <v>50</v>
@@ -58138,10 +58003,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="163" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D14" s="164" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E14" s="160" t="s">
         <v>50</v>
@@ -58174,10 +58039,10 @@
         <v>10</v>
       </c>
       <c r="C15" s="163" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D15" s="164" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E15" s="160" t="s">
         <v>50</v>
@@ -58210,10 +58075,10 @@
         <v>11</v>
       </c>
       <c r="C16" s="163" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D16" s="164" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E16" s="160" t="s">
         <v>50</v>
